--- a/Catalogo_Productos.xlsx
+++ b/Catalogo_Productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bonny Rodriguez\Desktop\App_chifa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F54F19-2626-4CBA-ADA9-DA6F00CACE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741A984E-2FFB-4C53-BB95-34E9B6AB3C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" xr2:uid="{7701F3F5-2ED2-4A4E-974A-8765CB3D8F1F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7701F3F5-2ED2-4A4E-974A-8765CB3D8F1F}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -55,15 +55,9 @@
     <t>COMBO 3</t>
   </si>
   <si>
-    <t>Enrollado de Pollo c/ OstiÃ³n y Pollo con Durazno</t>
-  </si>
-  <si>
     <t>COMBO 4</t>
   </si>
   <si>
-    <t>4 Alitas con Verduras y 4 Alitas con PiÃ±a</t>
-  </si>
-  <si>
     <t>ALITAS REBOZADAS 4 PZS</t>
   </si>
   <si>
@@ -97,21 +91,12 @@
     <t>ALITAS CON TAMARINDO</t>
   </si>
   <si>
-    <t>ALITAS CON PIÃ‘A</t>
-  </si>
-  <si>
-    <t>ALITAS EN SALSA OSTIÃ“N</t>
-  </si>
-  <si>
     <t>ALITAS TAUSI</t>
   </si>
   <si>
     <t>ALITAS CON DURAZNO</t>
   </si>
   <si>
-    <t>ALITAS CON PIÃ‘A Y DURAZNO</t>
-  </si>
-  <si>
     <t>ALITAS BELI BELI</t>
   </si>
   <si>
@@ -172,9 +157,6 @@
     <t>CHAUFA DE POLLO</t>
   </si>
   <si>
-    <t>Arroz chaufa clÃ¡sico</t>
-  </si>
-  <si>
     <t>CHAUFA</t>
   </si>
   <si>
@@ -214,9 +196,6 @@
     <t>CHAUFA DE LANGOSTINOS</t>
   </si>
   <si>
-    <t>CHAUFA DE POLLO CON CHAMPIÃ‘ONES</t>
-  </si>
-  <si>
     <t>CHAUFA SAM SEM</t>
   </si>
   <si>
@@ -235,21 +214,12 @@
     <t>CHAUFA FAMILIAR</t>
   </si>
   <si>
-    <t>PorciÃ³n grande para compartir</t>
-  </si>
-  <si>
     <t>CHAUFA ESPECIAL FAMILIAR</t>
   </si>
   <si>
-    <t>PorciÃ³n grande especial</t>
-  </si>
-  <si>
     <t>AEROPUERTO DE POLLO</t>
   </si>
   <si>
-    <t>CombinaciÃ³n clÃ¡sica de chaufa y tallarÃ­n</t>
-  </si>
-  <si>
     <t>AEROPUERTO</t>
   </si>
   <si>
@@ -268,9 +238,6 @@
     <t>AEROPUERTO SUPER ESPECIAL</t>
   </si>
   <si>
-    <t>AEROPUERTO DE POLLO CON CHAMPIÃ‘ONES</t>
-  </si>
-  <si>
     <t>AEROPUERTO DE LANGOSTINOS</t>
   </si>
   <si>
@@ -289,9 +256,6 @@
     <t>COMBINADO DE POLLO</t>
   </si>
   <si>
-    <t>Chaufa y tallarÃ­n saltado</t>
-  </si>
-  <si>
     <t>COMBINADOS</t>
   </si>
   <si>
@@ -379,9 +343,6 @@
     <t>TALLARIN SALTADO DE LANGOSTINOS</t>
   </si>
   <si>
-    <t>TALLARIN SALTADO DE POLLO CON CHAMPIÃ‘ONES</t>
-  </si>
-  <si>
     <t>TALLARIN SALTADO SAMSEM</t>
   </si>
   <si>
@@ -436,9 +397,6 @@
     <t>LIMON KAY + CHAUFA</t>
   </si>
   <si>
-    <t>Pollo crujiente en salsa de limÃ³n</t>
-  </si>
-  <si>
     <t>POLLO CON TAMARINDO + CHAUFA</t>
   </si>
   <si>
@@ -448,9 +406,6 @@
     <t>PLATOS DULCE</t>
   </si>
   <si>
-    <t>POLLO CON PIÃ‘A + CHAUFA</t>
-  </si>
-  <si>
     <t>POLLO CON DURAZNO + CHAUFA</t>
   </si>
   <si>
@@ -505,9 +460,6 @@
     <t>ENROLLADO DE POLLO CON TAUSI</t>
   </si>
   <si>
-    <t>ENROLLADO DE POLLO CON PIÃ‘A</t>
-  </si>
-  <si>
     <t>ENROLLADO DE POLLO CON VERDURA</t>
   </si>
   <si>
@@ -517,9 +469,6 @@
     <t>ENROLLADO DE POLLO EN SALSA BLANCA</t>
   </si>
   <si>
-    <t>ENROLLADO DE POLLO CON PIÃ‘A Y DURAZNO</t>
-  </si>
-  <si>
     <t>ENROLLADO DE POLLO ESPECIAL</t>
   </si>
   <si>
@@ -553,9 +502,6 @@
     <t>RES CON BROCOLI</t>
   </si>
   <si>
-    <t>RES CON CHAMPIÃ‘ONES</t>
-  </si>
-  <si>
     <t>LANGOSTINOS CON VERDURA</t>
   </si>
   <si>
@@ -592,15 +538,9 @@
     <t>PATO AGRIDULCE</t>
   </si>
   <si>
-    <t>PATO CON PIÃ‘A</t>
-  </si>
-  <si>
     <t>PATO CON CHAMPIÃ‘ONES</t>
   </si>
   <si>
-    <t>PATO CON PIÃ‘A Y DURAZNO</t>
-  </si>
-  <si>
     <t>CHICHARRON DE POLLO</t>
   </si>
   <si>
@@ -631,9 +571,6 @@
     <t>COSTILLA FRITA</t>
   </si>
   <si>
-    <t>Incluye Chaufa, PlÃ¡tano y Ensalada</t>
-  </si>
-  <si>
     <t>COSTILLAS</t>
   </si>
   <si>
@@ -643,39 +580,15 @@
     <t>Costillas sabrosas de la casa</t>
   </si>
   <si>
-    <t>PORCIÃ“N DE CHAUFA</t>
-  </si>
-  <si>
-    <t>GuarniciÃ³n adicional</t>
-  </si>
-  <si>
     <t>PORCIONES</t>
   </si>
   <si>
-    <t>PORCIÃ“N DE ARROZ BLANCO</t>
-  </si>
-  <si>
-    <t>PORCIÃ“N AEROPUERTO</t>
-  </si>
-  <si>
     <t>DOCENA DE WANTAN FRITO</t>
   </si>
   <si>
-    <t>AcompaÃ±amiento crujiente</t>
-  </si>
-  <si>
     <t>MEDIA DOCENA DE WANTAN FRITO</t>
   </si>
   <si>
-    <t>PORCIÃ“N DE PAPAS FRITAS</t>
-  </si>
-  <si>
-    <t>PORCIÃ“N DE PLATANO FRITO</t>
-  </si>
-  <si>
-    <t>PORCIÃ“N DE MADURO FRITO</t>
-  </si>
-  <si>
     <t>HUEVO</t>
   </si>
   <si>
@@ -688,18 +601,9 @@
     <t>Bebida refrescante tradicional</t>
   </si>
   <si>
-    <t>BEBIDAS FRÃAS</t>
-  </si>
-  <si>
-    <t>JARRA MARACUYÃ</t>
-  </si>
-  <si>
     <t>1/2 CHICHA MORADA</t>
   </si>
   <si>
-    <t>1/2 MARACUYÃ</t>
-  </si>
-  <si>
     <t>INKA/COCA DESCARTABLE PERSONAL</t>
   </si>
   <si>
@@ -739,15 +643,9 @@
     <t>TE</t>
   </si>
   <si>
-    <t>Canela y clavo, anÃ­s y manzanilla</t>
-  </si>
-  <si>
     <t>BEBIDAS CALIENTES</t>
   </si>
   <si>
-    <t>CAFÃ‰</t>
-  </si>
-  <si>
     <t>Bebida caliente</t>
   </si>
   <si>
@@ -764,6 +662,108 @@
   </si>
   <si>
     <t>ALITAS ACEVICHADAS</t>
+  </si>
+  <si>
+    <t>BEBIDAS FRÍAS</t>
+  </si>
+  <si>
+    <t>Canela y clavo, anÍ­s y manzanilla</t>
+  </si>
+  <si>
+    <t>Guarnición adicional</t>
+  </si>
+  <si>
+    <t>Acompañamiento crujiente</t>
+  </si>
+  <si>
+    <t>PORCIÓN DE PAPAS FRITAS</t>
+  </si>
+  <si>
+    <t>PORCIÓN DE PLATANO FRITO</t>
+  </si>
+  <si>
+    <t>PORCIÓN DE MADURO FRITO</t>
+  </si>
+  <si>
+    <t>PORCIÓN DE CHAUFA</t>
+  </si>
+  <si>
+    <t>PORCIÓN DE ARROZ BLANCO</t>
+  </si>
+  <si>
+    <t>PORCIÓN AEROPUERTO</t>
+  </si>
+  <si>
+    <t>Enrollado de Pollo c/ Ostión y Pollo con Durazno</t>
+  </si>
+  <si>
+    <t>ALITAS CONPIÑA</t>
+  </si>
+  <si>
+    <t>POLLO CONPIÑA + CHAUFA</t>
+  </si>
+  <si>
+    <t>ENROLLADO DE POLLO CONPIÑA</t>
+  </si>
+  <si>
+    <t>ENROLLADO DE POLLO CONPIÑA Y DURAZNO</t>
+  </si>
+  <si>
+    <t>PATO CONPIÑA</t>
+  </si>
+  <si>
+    <t>PATO CONPIÑA Y DURAZNO</t>
+  </si>
+  <si>
+    <t>4 Alitas con Verduras y 4 Alitas con Piña</t>
+  </si>
+  <si>
+    <t>ALITAS CON PIÑA Y DURAZNO</t>
+  </si>
+  <si>
+    <t>ALITAS EN SALSAOSTIÓN</t>
+  </si>
+  <si>
+    <t>Arroz chaufa clásico</t>
+  </si>
+  <si>
+    <t>CHAUFA DE POLLO CON CHAMPIÑONES</t>
+  </si>
+  <si>
+    <t>Porción grande para compartir</t>
+  </si>
+  <si>
+    <t>Porción grande especial</t>
+  </si>
+  <si>
+    <t>Pollo crujiente en salsa de limón</t>
+  </si>
+  <si>
+    <t>Incluye Chaufa, Plátano y Ensalada</t>
+  </si>
+  <si>
+    <t>AEROPUERTO DE POLLO CON CHAMPIÑONES</t>
+  </si>
+  <si>
+    <t>Combinación clásica de chaufa y tallarín</t>
+  </si>
+  <si>
+    <t>Chaufa y tallarín saltado</t>
+  </si>
+  <si>
+    <t>TALLARIN SALTADO DE POLLO CON CHAMPIÑONES</t>
+  </si>
+  <si>
+    <t>RES CON CHAMPIÑONES</t>
+  </si>
+  <si>
+    <t>CAFÉ</t>
+  </si>
+  <si>
+    <t>1/2 MARACUYÁ</t>
+  </si>
+  <si>
+    <t>JARRA MARACUYÁ</t>
   </si>
 </sst>
 </file>
@@ -1607,8 +1607,8 @@
   <dimension ref="A1:E172"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.44140625" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" customWidth="1"/>
+    <col min="2" max="2" width="39.88671875" customWidth="1"/>
+    <col min="3" max="3" width="54.21875" customWidth="1"/>
     <col min="5" max="5" width="20.77734375" customWidth="1"/>
     <col min="6" max="6" width="39.5546875" customWidth="1"/>
   </cols>
@@ -1672,7 +1672,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="D4">
         <v>37</v>
@@ -1686,10 +1686,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>231</v>
       </c>
       <c r="D5">
         <v>35</v>
@@ -1703,16 +1703,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1720,16 +1720,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1737,16 +1737,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8">
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1754,16 +1754,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1771,16 +1771,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10">
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1788,16 +1788,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11">
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1805,16 +1805,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1822,16 +1822,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13">
         <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1839,16 +1839,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D14">
         <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1856,16 +1856,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>233</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D15">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1873,16 +1873,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D16">
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1890,16 +1890,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1907,16 +1907,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1924,16 +1924,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D19">
         <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1941,16 +1941,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D20">
         <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1958,16 +1958,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D21">
         <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1975,16 +1975,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22">
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1992,16 +1992,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D23">
         <v>17</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -2009,16 +2009,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D24">
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -2026,16 +2026,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D25">
         <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -2043,16 +2043,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D26">
         <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -2060,16 +2060,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D27">
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -2077,16 +2077,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D28">
         <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -2094,16 +2094,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D29">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -2111,16 +2111,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D30">
         <v>19</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -2128,16 +2128,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D31">
         <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -2145,16 +2145,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D32">
         <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -2162,16 +2162,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D33">
         <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2179,16 +2179,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D34">
         <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2196,16 +2196,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D35">
         <v>29</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2213,16 +2213,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D36">
         <v>17</v>
       </c>
       <c r="E36" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2230,16 +2230,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D37">
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2247,16 +2247,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D38">
         <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2264,16 +2264,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D39">
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2281,16 +2281,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D40">
         <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2298,16 +2298,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D41">
         <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2315,16 +2315,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D42">
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2332,16 +2332,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D43">
         <v>27</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2349,16 +2349,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D44">
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -2366,16 +2366,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D45">
         <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2383,16 +2383,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D46">
         <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2400,16 +2400,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D47">
         <v>32</v>
       </c>
       <c r="E47" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2417,16 +2417,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D48">
         <v>27</v>
       </c>
       <c r="E48" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -2434,16 +2434,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>235</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D49">
         <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -2451,16 +2451,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D50">
         <v>27</v>
       </c>
       <c r="E50" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -2468,16 +2468,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D51">
         <v>27</v>
       </c>
       <c r="E51" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -2485,16 +2485,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="D52">
         <v>32</v>
       </c>
       <c r="E52" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -2502,16 +2502,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D53">
         <v>36</v>
       </c>
       <c r="E53" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -2519,16 +2519,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>71</v>
+        <v>236</v>
       </c>
       <c r="D54">
         <v>51</v>
       </c>
       <c r="E54" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -2536,16 +2536,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>73</v>
+        <v>237</v>
       </c>
       <c r="D55">
         <v>69</v>
       </c>
       <c r="E55" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -2553,16 +2553,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D56">
         <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -2570,16 +2570,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C57" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D57">
         <v>22</v>
       </c>
       <c r="E57" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -2587,16 +2587,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D58">
         <v>22</v>
       </c>
       <c r="E58" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -2604,16 +2604,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C59" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D59">
         <v>22</v>
       </c>
       <c r="E59" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -2621,16 +2621,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="C60" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D60">
         <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -2638,16 +2638,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D61">
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -2655,16 +2655,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C62" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D62">
         <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -2672,16 +2672,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="C63" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D63">
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -2689,16 +2689,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D64">
         <v>30</v>
       </c>
       <c r="E64" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -2706,16 +2706,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D65">
         <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -2723,16 +2723,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D66">
         <v>28</v>
       </c>
       <c r="E66" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -2740,16 +2740,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D67">
         <v>28</v>
       </c>
       <c r="E67" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -2757,16 +2757,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="D68">
         <v>33</v>
       </c>
       <c r="E68" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -2774,16 +2774,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D69">
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2791,16 +2791,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D70">
         <v>22</v>
       </c>
       <c r="E70" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2808,16 +2808,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D71">
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -2825,16 +2825,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D72">
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -2842,16 +2842,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C73" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D73">
         <v>22</v>
       </c>
       <c r="E73" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -2859,16 +2859,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D74">
         <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -2876,16 +2876,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D75">
         <v>25</v>
       </c>
       <c r="E75" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -2893,16 +2893,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D76">
         <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2910,16 +2910,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D77">
         <v>22</v>
       </c>
       <c r="E77" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2927,16 +2927,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C78" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D78">
         <v>30</v>
       </c>
       <c r="E78" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C79" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D79">
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -2961,16 +2961,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C80" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D80">
         <v>31</v>
       </c>
       <c r="E80" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2978,16 +2978,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C81" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D81">
         <v>22</v>
       </c>
       <c r="E81" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2995,16 +2995,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C82" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D82">
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -3012,16 +3012,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C83" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D83">
         <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -3029,16 +3029,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C84" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D84">
         <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -3046,16 +3046,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C85" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D85">
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -3063,16 +3063,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C86" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D86">
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -3080,16 +3080,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D87">
         <v>22</v>
       </c>
       <c r="E87" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -3097,16 +3097,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C88" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D88">
         <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -3114,16 +3114,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C89" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D89">
         <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -3131,16 +3131,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C90" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D90">
         <v>27</v>
       </c>
       <c r="E90" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -3148,16 +3148,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D91">
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -3165,16 +3165,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C92" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D92">
         <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -3182,16 +3182,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C93" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D93">
         <v>29</v>
       </c>
       <c r="E93" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -3199,16 +3199,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>119</v>
+        <v>243</v>
       </c>
       <c r="C94" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D94">
         <v>25</v>
       </c>
       <c r="E94" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -3216,16 +3216,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C95" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D95">
         <v>29</v>
       </c>
       <c r="E95" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -3233,16 +3233,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D96">
         <v>22</v>
       </c>
       <c r="E96" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -3250,16 +3250,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D97">
         <v>30</v>
       </c>
       <c r="E97" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -3267,16 +3267,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C98" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D98">
         <v>26</v>
       </c>
       <c r="E98" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -3284,16 +3284,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C99" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D99">
         <v>38</v>
       </c>
       <c r="E99" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -3301,16 +3301,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C100" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D100">
         <v>20</v>
       </c>
       <c r="E100" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -3318,16 +3318,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C101" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D101">
         <v>22</v>
       </c>
       <c r="E101" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -3335,16 +3335,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C102" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D102">
         <v>29</v>
       </c>
       <c r="E102" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -3352,16 +3352,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C103" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D103">
         <v>25</v>
       </c>
       <c r="E103" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -3369,16 +3369,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C104" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D104">
         <v>26</v>
       </c>
       <c r="E104" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -3386,16 +3386,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C105" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D105">
         <v>24</v>
       </c>
       <c r="E105" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -3403,16 +3403,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="C106" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D106">
         <v>26</v>
       </c>
       <c r="E106" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -3420,16 +3420,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C107" t="s">
-        <v>138</v>
+        <v>238</v>
       </c>
       <c r="D107">
         <v>27</v>
       </c>
       <c r="E107" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -3437,16 +3437,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C108" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D108">
         <v>22</v>
       </c>
       <c r="E108" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -3454,16 +3454,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
       <c r="C109" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D109">
         <v>22</v>
       </c>
       <c r="E109" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -3471,16 +3471,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C110" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D110">
         <v>22</v>
       </c>
       <c r="E110" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -3488,16 +3488,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="C111" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D111">
         <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -3505,16 +3505,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C112" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D112">
         <v>27</v>
       </c>
       <c r="E112" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -3522,16 +3522,16 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C113" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="D113">
         <v>27</v>
       </c>
       <c r="E113" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -3539,16 +3539,16 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C114" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D114">
         <v>20</v>
       </c>
       <c r="E114" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -3556,16 +3556,16 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C115" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D115">
         <v>20</v>
       </c>
       <c r="E115" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -3573,16 +3573,16 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="C116" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D116">
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -3590,16 +3590,16 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C117" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D117">
         <v>29</v>
       </c>
       <c r="E117" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -3607,16 +3607,16 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C118" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D118">
         <v>30</v>
       </c>
       <c r="E118" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -3624,16 +3624,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C119" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D119">
         <v>28</v>
       </c>
       <c r="E119" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -3641,16 +3641,16 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C120" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D120">
         <v>28</v>
       </c>
       <c r="E120" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -3658,16 +3658,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="C121" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D121">
         <v>28</v>
       </c>
       <c r="E121" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -3675,16 +3675,16 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="C122" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D122">
         <v>28</v>
       </c>
       <c r="E122" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -3692,16 +3692,16 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D123">
         <v>28</v>
       </c>
       <c r="E123" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -3709,16 +3709,16 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D124">
         <v>28</v>
       </c>
       <c r="E124" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -3726,16 +3726,16 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D125">
         <v>30</v>
       </c>
       <c r="E125" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -3743,16 +3743,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="C126" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D126">
         <v>32</v>
       </c>
       <c r="E126" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
@@ -3760,16 +3760,16 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="C127" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D127">
         <v>32</v>
       </c>
       <c r="E127" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -3777,16 +3777,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="C128" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="D128">
         <v>38</v>
       </c>
       <c r="E128" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -3794,16 +3794,16 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="D129">
         <v>39</v>
       </c>
       <c r="E129" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -3811,16 +3811,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="C130" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="D130">
         <v>38</v>
       </c>
       <c r="E130" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -3828,16 +3828,16 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="C131" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="D131">
         <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -3845,16 +3845,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="C132" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="D132">
         <v>24</v>
       </c>
       <c r="E132" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -3862,16 +3862,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="C133" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="D133">
         <v>26</v>
       </c>
       <c r="E133" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -3879,16 +3879,16 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="C134" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="D134">
         <v>30</v>
       </c>
       <c r="E134" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -3896,16 +3896,16 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="C135" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="D135">
         <v>32</v>
       </c>
       <c r="E135" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -3913,16 +3913,16 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="C136" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="D136">
         <v>38</v>
       </c>
       <c r="E136" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -3930,16 +3930,16 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="C137" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="D137">
         <v>30</v>
       </c>
       <c r="E137" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -3947,16 +3947,16 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="C138" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="D138">
         <v>30</v>
       </c>
       <c r="E138" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
@@ -3964,16 +3964,16 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="C139" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="D139">
         <v>30</v>
       </c>
       <c r="E139" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -3981,16 +3981,16 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="C140" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="D140">
         <v>30</v>
       </c>
       <c r="E140" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
@@ -3998,16 +3998,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="C141" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="D141">
         <v>30</v>
       </c>
       <c r="E141" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -4015,16 +4015,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="C142" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="D142">
         <v>30</v>
       </c>
       <c r="E142" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -4032,16 +4032,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="C143" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="D143">
         <v>32</v>
       </c>
       <c r="E143" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -4049,16 +4049,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="C144" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D144">
         <v>26</v>
       </c>
       <c r="E144" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
@@ -4066,16 +4066,16 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="C145" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D145">
         <v>32</v>
       </c>
       <c r="E145" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
@@ -4083,16 +4083,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="C146" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D146">
         <v>22</v>
       </c>
       <c r="E146" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
@@ -4100,16 +4100,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C147" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D147">
         <v>24</v>
       </c>
       <c r="E147" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
@@ -4117,16 +4117,16 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="C148" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D148">
         <v>27</v>
       </c>
       <c r="E148" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
@@ -4134,16 +4134,16 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="C149" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="D149">
         <v>33</v>
       </c>
       <c r="E149" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
@@ -4151,16 +4151,16 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C150" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="D150">
         <v>33</v>
       </c>
       <c r="E150" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
@@ -4168,16 +4168,16 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C151" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D151">
         <v>12</v>
       </c>
       <c r="E151" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
@@ -4185,16 +4185,16 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="C152" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D152">
         <v>7</v>
       </c>
       <c r="E152" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
@@ -4202,16 +4202,16 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C153" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D153">
         <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
@@ -4219,16 +4219,16 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="C154" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D154">
         <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
@@ -4236,16 +4236,16 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="C155" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D155">
         <v>5</v>
       </c>
       <c r="E155" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
@@ -4253,16 +4253,16 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C156" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D156">
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
@@ -4270,16 +4270,16 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>219</v>
+      </c>
+      <c r="C157" t="s">
         <v>216</v>
-      </c>
-      <c r="C157" t="s">
-        <v>208</v>
       </c>
       <c r="D157">
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
@@ -4287,16 +4287,16 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C158" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D158">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
@@ -4304,16 +4304,16 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="C159" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="D159">
         <v>3</v>
       </c>
       <c r="E159" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
@@ -4321,16 +4321,16 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="C160" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="D160">
         <v>13</v>
       </c>
       <c r="E160" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
@@ -4338,16 +4338,16 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="C161" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="D161">
         <v>11</v>
       </c>
       <c r="E161" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
@@ -4355,16 +4355,16 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="C162" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="D162">
         <v>7</v>
       </c>
       <c r="E162" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
@@ -4372,16 +4372,16 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="C163" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="D163">
         <v>6</v>
       </c>
       <c r="E163" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
@@ -4389,16 +4389,16 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="C164" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="D164">
         <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
@@ -4406,16 +4406,16 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="C165" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="D165">
         <v>6</v>
       </c>
       <c r="E165" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
@@ -4423,16 +4423,16 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="C166" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="D166">
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
@@ -4440,16 +4440,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="C167" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="D167">
         <v>15</v>
       </c>
       <c r="E167" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
@@ -4457,16 +4457,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="C168" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="D168">
         <v>17</v>
       </c>
       <c r="E168" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
@@ -4474,16 +4474,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="C169" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="D169">
         <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
@@ -4491,16 +4491,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="C170" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="D170">
         <v>4</v>
       </c>
       <c r="E170" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
@@ -4508,16 +4508,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C171" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="D171">
         <v>5</v>
       </c>
       <c r="E171" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
@@ -4525,16 +4525,16 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="C172" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D172">
         <v>26</v>
       </c>
       <c r="E172" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Catalogo_Productos.xlsx
+++ b/Catalogo_Productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bonny Rodriguez\Desktop\App_chifa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741A984E-2FFB-4C53-BB95-34E9B6AB3C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1EB4CE-8846-4A91-BBD6-2A1D6CF72622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7701F3F5-2ED2-4A4E-974A-8765CB3D8F1F}"/>
   </bookViews>
@@ -379,9 +379,6 @@
     <t>POLLO CON VERDURA ESPECIAL + CHAUFA</t>
   </si>
   <si>
-    <t>POLLO CON CHAMPIÃ‘ONES + CHAUFA</t>
-  </si>
-  <si>
     <t>POLLO EN TROZOS CON VERDURA + CHAUFA</t>
   </si>
   <si>
@@ -403,9 +400,6 @@
     <t>Platos agridulces tradicionales</t>
   </si>
   <si>
-    <t>PLATOS DULCE</t>
-  </si>
-  <si>
     <t>POLLO CON DURAZNO + CHAUFA</t>
   </si>
   <si>
@@ -764,6 +758,12 @@
   </si>
   <si>
     <t>JARRA MARACUYÁ</t>
+  </si>
+  <si>
+    <t>POLLO CON CHAMPIÑONES + CHAUFA</t>
+  </si>
+  <si>
+    <t>PLATOS DULCES</t>
   </si>
 </sst>
 </file>
@@ -1672,7 +1672,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D4">
         <v>37</v>
@@ -1689,7 +1689,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D5">
         <v>35</v>
@@ -1703,7 +1703,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -1754,7 +1754,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -1839,7 +1839,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
@@ -1856,7 +1856,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C15" t="s">
         <v>21</v>
@@ -1907,7 +1907,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
@@ -1941,7 +1941,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
@@ -2216,7 +2216,7 @@
         <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D36">
         <v>17</v>
@@ -2233,7 +2233,7 @@
         <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D37">
         <v>20</v>
@@ -2250,7 +2250,7 @@
         <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D38">
         <v>21</v>
@@ -2267,7 +2267,7 @@
         <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D39">
         <v>21</v>
@@ -2284,7 +2284,7 @@
         <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D40">
         <v>22</v>
@@ -2301,7 +2301,7 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D41">
         <v>23</v>
@@ -2318,7 +2318,7 @@
         <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D42">
         <v>22</v>
@@ -2335,7 +2335,7 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D43">
         <v>27</v>
@@ -2352,7 +2352,7 @@
         <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D44">
         <v>24</v>
@@ -2369,7 +2369,7 @@
         <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D45">
         <v>27</v>
@@ -2386,7 +2386,7 @@
         <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D46">
         <v>27</v>
@@ -2403,7 +2403,7 @@
         <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D47">
         <v>32</v>
@@ -2420,7 +2420,7 @@
         <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D48">
         <v>27</v>
@@ -2434,10 +2434,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C49" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D49">
         <v>25</v>
@@ -2454,7 +2454,7 @@
         <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D50">
         <v>27</v>
@@ -2471,7 +2471,7 @@
         <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D51">
         <v>27</v>
@@ -2488,7 +2488,7 @@
         <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D52">
         <v>32</v>
@@ -2522,7 +2522,7 @@
         <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D54">
         <v>51</v>
@@ -2539,7 +2539,7 @@
         <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D55">
         <v>69</v>
@@ -2556,7 +2556,7 @@
         <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D56">
         <v>20</v>
@@ -2573,7 +2573,7 @@
         <v>67</v>
       </c>
       <c r="C57" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D57">
         <v>22</v>
@@ -2590,7 +2590,7 @@
         <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D58">
         <v>22</v>
@@ -2607,7 +2607,7 @@
         <v>69</v>
       </c>
       <c r="C59" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D59">
         <v>22</v>
@@ -2621,10 +2621,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C60" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D60">
         <v>23</v>
@@ -2641,7 +2641,7 @@
         <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D61">
         <v>25</v>
@@ -2658,7 +2658,7 @@
         <v>71</v>
       </c>
       <c r="C62" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D62">
         <v>34</v>
@@ -2672,10 +2672,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D63">
         <v>25</v>
@@ -2692,7 +2692,7 @@
         <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D64">
         <v>30</v>
@@ -2709,7 +2709,7 @@
         <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D65">
         <v>22</v>
@@ -2726,7 +2726,7 @@
         <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D66">
         <v>28</v>
@@ -2743,7 +2743,7 @@
         <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D67">
         <v>28</v>
@@ -2760,7 +2760,7 @@
         <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D68">
         <v>33</v>
@@ -2777,7 +2777,7 @@
         <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D69">
         <v>20</v>
@@ -2794,7 +2794,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D70">
         <v>22</v>
@@ -2811,7 +2811,7 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D71">
         <v>24</v>
@@ -2828,7 +2828,7 @@
         <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D72">
         <v>24</v>
@@ -2845,7 +2845,7 @@
         <v>82</v>
       </c>
       <c r="C73" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D73">
         <v>22</v>
@@ -2862,7 +2862,7 @@
         <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D74">
         <v>30</v>
@@ -2879,7 +2879,7 @@
         <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D75">
         <v>25</v>
@@ -2896,7 +2896,7 @@
         <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D76">
         <v>29</v>
@@ -2913,7 +2913,7 @@
         <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D77">
         <v>22</v>
@@ -2930,7 +2930,7 @@
         <v>87</v>
       </c>
       <c r="C78" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D78">
         <v>30</v>
@@ -2947,7 +2947,7 @@
         <v>88</v>
       </c>
       <c r="C79" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D79">
         <v>29</v>
@@ -2964,7 +2964,7 @@
         <v>89</v>
       </c>
       <c r="C80" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D80">
         <v>31</v>
@@ -3199,7 +3199,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C94" t="s">
         <v>98</v>
@@ -3352,7 +3352,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="C103" t="s">
         <v>115</v>
@@ -3369,7 +3369,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C104" t="s">
         <v>115</v>
@@ -3386,7 +3386,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C105" t="s">
         <v>115</v>
@@ -3403,10 +3403,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>121</v>
+      </c>
+      <c r="C106" t="s">
         <v>122</v>
-      </c>
-      <c r="C106" t="s">
-        <v>123</v>
       </c>
       <c r="D106">
         <v>26</v>
@@ -3420,10 +3420,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C107" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D107">
         <v>27</v>
@@ -3437,16 +3437,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>124</v>
+      </c>
+      <c r="C108" t="s">
         <v>125</v>
-      </c>
-      <c r="C108" t="s">
-        <v>126</v>
       </c>
       <c r="D108">
         <v>22</v>
       </c>
       <c r="E108" t="s">
-        <v>127</v>
+        <v>247</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -3454,16 +3454,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C109" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D109">
         <v>22</v>
       </c>
       <c r="E109" t="s">
-        <v>127</v>
+        <v>247</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -3471,16 +3471,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C110" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D110">
         <v>22</v>
       </c>
       <c r="E110" t="s">
-        <v>127</v>
+        <v>247</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -3488,16 +3488,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C111" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D111">
         <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>127</v>
+        <v>247</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -3505,16 +3505,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C112" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D112">
         <v>27</v>
       </c>
       <c r="E112" t="s">
-        <v>127</v>
+        <v>247</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -3522,16 +3522,16 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C113" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D113">
         <v>27</v>
       </c>
       <c r="E113" t="s">
-        <v>127</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -3539,16 +3539,16 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C114" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D114">
         <v>20</v>
       </c>
       <c r="E114" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -3556,16 +3556,16 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C115" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D115">
         <v>20</v>
       </c>
       <c r="E115" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -3573,16 +3573,16 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C116" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D116">
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -3590,16 +3590,16 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C117" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D117">
         <v>29</v>
       </c>
       <c r="E117" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -3607,16 +3607,16 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C118" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D118">
         <v>30</v>
       </c>
       <c r="E118" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -3624,16 +3624,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C119" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D119">
         <v>28</v>
       </c>
       <c r="E119" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -3641,16 +3641,16 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C120" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D120">
         <v>28</v>
       </c>
       <c r="E120" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -3658,16 +3658,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C121" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D121">
         <v>28</v>
       </c>
       <c r="E121" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -3675,16 +3675,16 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C122" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D122">
         <v>28</v>
       </c>
       <c r="E122" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -3692,16 +3692,16 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C123" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D123">
         <v>28</v>
       </c>
       <c r="E123" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -3709,16 +3709,16 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C124" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D124">
         <v>28</v>
       </c>
       <c r="E124" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -3726,16 +3726,16 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C125" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D125">
         <v>30</v>
       </c>
       <c r="E125" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -3743,16 +3743,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C126" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D126">
         <v>32</v>
       </c>
       <c r="E126" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
@@ -3760,16 +3760,16 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C127" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D127">
         <v>32</v>
       </c>
       <c r="E127" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -3777,16 +3777,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C128" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D128">
         <v>38</v>
       </c>
       <c r="E128" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -3794,16 +3794,16 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C129" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D129">
         <v>39</v>
       </c>
       <c r="E129" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -3811,16 +3811,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C130" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D130">
         <v>38</v>
       </c>
       <c r="E130" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -3828,16 +3828,16 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D131">
         <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -3845,16 +3845,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C132" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D132">
         <v>24</v>
       </c>
       <c r="E132" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -3862,16 +3862,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C133" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D133">
         <v>26</v>
       </c>
       <c r="E133" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -3879,16 +3879,16 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C134" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D134">
         <v>30</v>
       </c>
       <c r="E134" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -3896,16 +3896,16 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C135" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D135">
         <v>32</v>
       </c>
       <c r="E135" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -3913,16 +3913,16 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C136" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D136">
         <v>38</v>
       </c>
       <c r="E136" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -3930,16 +3930,16 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C137" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D137">
         <v>30</v>
       </c>
       <c r="E137" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -3947,16 +3947,16 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C138" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D138">
         <v>30</v>
       </c>
       <c r="E138" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
@@ -3964,16 +3964,16 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C139" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D139">
         <v>30</v>
       </c>
       <c r="E139" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -3981,16 +3981,16 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C140" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D140">
         <v>30</v>
       </c>
       <c r="E140" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
@@ -3998,16 +3998,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C141" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D141">
         <v>30</v>
       </c>
       <c r="E141" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -4015,16 +4015,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C142" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D142">
         <v>30</v>
       </c>
       <c r="E142" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -4032,16 +4032,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C143" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D143">
         <v>32</v>
       </c>
       <c r="E143" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -4049,16 +4049,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C144" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D144">
         <v>26</v>
       </c>
       <c r="E144" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
@@ -4066,16 +4066,16 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C145" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D145">
         <v>32</v>
       </c>
       <c r="E145" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
@@ -4083,16 +4083,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C146" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D146">
         <v>22</v>
       </c>
       <c r="E146" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
@@ -4100,16 +4100,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C147" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D147">
         <v>24</v>
       </c>
       <c r="E147" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
@@ -4117,16 +4117,16 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C148" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D148">
         <v>27</v>
       </c>
       <c r="E148" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
@@ -4134,16 +4134,16 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C149" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D149">
         <v>33</v>
       </c>
       <c r="E149" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
@@ -4151,16 +4151,16 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C150" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D150">
         <v>33</v>
       </c>
       <c r="E150" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
@@ -4168,16 +4168,16 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C151" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D151">
         <v>12</v>
       </c>
       <c r="E151" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
@@ -4185,16 +4185,16 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C152" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D152">
         <v>7</v>
       </c>
       <c r="E152" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
@@ -4202,16 +4202,16 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C153" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D153">
         <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
@@ -4219,16 +4219,16 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C154" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D154">
         <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
@@ -4236,16 +4236,16 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C155" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D155">
         <v>5</v>
       </c>
       <c r="E155" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
@@ -4253,16 +4253,16 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C156" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D156">
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
@@ -4270,16 +4270,16 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C157" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D157">
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
@@ -4287,16 +4287,16 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C158" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D158">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
@@ -4304,16 +4304,16 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C159" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D159">
         <v>3</v>
       </c>
       <c r="E159" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
@@ -4321,16 +4321,16 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C160" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D160">
         <v>13</v>
       </c>
       <c r="E160" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
@@ -4338,16 +4338,16 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C161" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D161">
         <v>11</v>
       </c>
       <c r="E161" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
@@ -4355,16 +4355,16 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C162" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D162">
         <v>7</v>
       </c>
       <c r="E162" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
@@ -4372,16 +4372,16 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C163" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D163">
         <v>6</v>
       </c>
       <c r="E163" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
@@ -4389,16 +4389,16 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C164" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D164">
         <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
@@ -4406,16 +4406,16 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C165" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D165">
         <v>6</v>
       </c>
       <c r="E165" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
@@ -4423,16 +4423,16 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C166" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D166">
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
@@ -4440,16 +4440,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C167" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D167">
         <v>15</v>
       </c>
       <c r="E167" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
@@ -4457,16 +4457,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C168" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D168">
         <v>17</v>
       </c>
       <c r="E168" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
@@ -4474,16 +4474,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C169" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D169">
         <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
@@ -4491,16 +4491,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C170" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D170">
         <v>4</v>
       </c>
       <c r="E170" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
@@ -4508,16 +4508,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C171" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D171">
         <v>5</v>
       </c>
       <c r="E171" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
@@ -4525,7 +4525,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C172" t="s">
         <v>17</v>

--- a/Catalogo_Productos.xlsx
+++ b/Catalogo_Productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bonny Rodriguez\Desktop\App_chifa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1EB4CE-8846-4A91-BBD6-2A1D6CF72622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038251D7-F34B-4972-B590-5DC69987A81C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7701F3F5-2ED2-4A4E-974A-8765CB3D8F1F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="209">
   <si>
     <t>ID</t>
   </si>
@@ -61,9 +61,6 @@
     <t>ALITAS REBOZADAS 4 PZS</t>
   </si>
   <si>
-    <t>Incluye Chaufa + Papas + Vinagreta</t>
-  </si>
-  <si>
     <t>ALITAS REBOZADAS</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
     <t>ALITAS EN SALSA BBQ</t>
   </si>
   <si>
-    <t>Incluye Chaufa + Papas + Ensalada</t>
-  </si>
-  <si>
     <t>ALITAS ESPECIALES</t>
   </si>
   <si>
@@ -85,9 +79,6 @@
     <t>ALITAS CON VERDURAS</t>
   </si>
   <si>
-    <t>Alitas especiales de la casa</t>
-  </si>
-  <si>
     <t>ALITAS CON TAMARINDO</t>
   </si>
   <si>
@@ -112,9 +103,6 @@
     <t>SOPA WANTAN DE POLLO</t>
   </si>
   <si>
-    <t>Sopa caliente tradicional</t>
-  </si>
-  <si>
     <t>SOPAS</t>
   </si>
   <si>
@@ -295,9 +283,6 @@
     <t>LOMO SALTADO DE POLLO</t>
   </si>
   <si>
-    <t>Saltado jugoso tradicional</t>
-  </si>
-  <si>
     <t>LOMOS SALTADOS</t>
   </si>
   <si>
@@ -316,9 +301,6 @@
     <t>TALLARIN SALTADO DE POLLO</t>
   </si>
   <si>
-    <t>Fideos saltados al wok</t>
-  </si>
-  <si>
     <t>TALLARINES SALTADOS</t>
   </si>
   <si>
@@ -349,27 +331,18 @@
     <t>TALLARIN FRITO DE POLLO</t>
   </si>
   <si>
-    <t>Fideos fritos estilo chifa</t>
-  </si>
-  <si>
     <t>TALLARIN FRITO ESPECIAL</t>
   </si>
   <si>
     <t>TALLARIN EN TROZOS CON VERDURA</t>
   </si>
   <si>
-    <t>Fideos estilo chifa</t>
-  </si>
-  <si>
     <t>TALLARIN TAYPA</t>
   </si>
   <si>
     <t>POLLO CON VERDURAS + CHAUFA</t>
   </si>
   <si>
-    <t>Platos salados tradicionales</t>
-  </si>
-  <si>
     <t>PLATOS SALADOS</t>
   </si>
   <si>
@@ -388,18 +361,12 @@
     <t>CHI JAU KAY + CHAUFA</t>
   </si>
   <si>
-    <t>Pollo crujiente en salsa salada</t>
-  </si>
-  <si>
     <t>LIMON KAY + CHAUFA</t>
   </si>
   <si>
     <t>POLLO CON TAMARINDO + CHAUFA</t>
   </si>
   <si>
-    <t>Platos agridulces tradicionales</t>
-  </si>
-  <si>
     <t>POLLO CON DURAZNO + CHAUFA</t>
   </si>
   <si>
@@ -409,21 +376,12 @@
     <t>KAM LU WANTAN + CHAUFA</t>
   </si>
   <si>
-    <t>Wantanes fritos con salsa agridulce y carnes</t>
-  </si>
-  <si>
     <t>TIPA KAY + CHAUFA</t>
   </si>
   <si>
-    <t>Pollo crujiente en salsa agridulce</t>
-  </si>
-  <si>
     <t>TORTILLA DE POLLO</t>
   </si>
   <si>
-    <t>Tortilla al estilo chifa</t>
-  </si>
-  <si>
     <t>TORTILLAS</t>
   </si>
   <si>
@@ -442,9 +400,6 @@
     <t>ENROLLADO DE POLLO CON OSTION</t>
   </si>
   <si>
-    <t>Enrollados sabrosos de la casa</t>
-  </si>
-  <si>
     <t>ENROLLADOS</t>
   </si>
   <si>
@@ -469,27 +424,15 @@
     <t>TAYPA</t>
   </si>
   <si>
-    <t>Especialidad taypa de la casa</t>
-  </si>
-  <si>
     <t>TAYPA A LA PLANCHA</t>
   </si>
   <si>
-    <t>Especialidad taypa caliente</t>
-  </si>
-  <si>
     <t>TAYPA DE LANGOSTINOS</t>
   </si>
   <si>
-    <t>Especialidad taypa marina</t>
-  </si>
-  <si>
     <t>RES CON VERDURA</t>
   </si>
   <si>
-    <t>Platos a base de carne de res</t>
-  </si>
-  <si>
     <t>RES</t>
   </si>
   <si>
@@ -499,9 +442,6 @@
     <t>LANGOSTINOS CON VERDURA</t>
   </si>
   <si>
-    <t>Platos marinos al wok</t>
-  </si>
-  <si>
     <t>LANGOSTINOS</t>
   </si>
   <si>
@@ -511,15 +451,9 @@
     <t>LANGOSTINOS A LA PLANCHA</t>
   </si>
   <si>
-    <t>Platos marinos calientes</t>
-  </si>
-  <si>
     <t>PATO CON VERDURA</t>
   </si>
   <si>
-    <t>Platos especiales de pato</t>
-  </si>
-  <si>
     <t>PATO</t>
   </si>
   <si>
@@ -532,15 +466,9 @@
     <t>PATO AGRIDULCE</t>
   </si>
   <si>
-    <t>PATO CON CHAMPIÃ‘ONES</t>
-  </si>
-  <si>
     <t>CHICHARRON DE POLLO</t>
   </si>
   <si>
-    <t>Crujiente y dorado</t>
-  </si>
-  <si>
     <t>CHICHARRONES</t>
   </si>
   <si>
@@ -550,9 +478,6 @@
     <t>CHANCHO CON TAMARINDO</t>
   </si>
   <si>
-    <t>Platos a base de carne de cerdo</t>
-  </si>
-  <si>
     <t>CHANCHO</t>
   </si>
   <si>
@@ -571,9 +496,6 @@
     <t>COSTILLA EN SALSA BBQ</t>
   </si>
   <si>
-    <t>Costillas sabrosas de la casa</t>
-  </si>
-  <si>
     <t>PORCIONES</t>
   </si>
   <si>
@@ -586,54 +508,30 @@
     <t>HUEVO</t>
   </si>
   <si>
-    <t>Adicional</t>
-  </si>
-  <si>
     <t>JARRA CHICHA MORADA</t>
   </si>
   <si>
-    <t>Bebida refrescante tradicional</t>
-  </si>
-  <si>
     <t>1/2 CHICHA MORADA</t>
   </si>
   <si>
     <t>INKA/COCA DESCARTABLE PERSONAL</t>
   </si>
   <si>
-    <t>Gaseosa individual</t>
-  </si>
-  <si>
     <t>INCA COLA GORDITA</t>
   </si>
   <si>
-    <t>Gaseosa familiar mediana</t>
-  </si>
-  <si>
     <t>INCA/COCA 1 LTS</t>
   </si>
   <si>
-    <t>Gaseosa familiar</t>
-  </si>
-  <si>
     <t>INCA/COCA 2.5 LTS</t>
   </si>
   <si>
-    <t>Gaseosa familiar grande</t>
-  </si>
-  <si>
     <t>INCA/COCA 3 LTS</t>
   </si>
   <si>
-    <t>Gaseosa familiar gigante</t>
-  </si>
-  <si>
     <t>CERVEZA</t>
   </si>
   <si>
-    <t>Bebida helada</t>
-  </si>
-  <si>
     <t>TE</t>
   </si>
   <si>
@@ -661,15 +559,6 @@
     <t>BEBIDAS FRÍAS</t>
   </si>
   <si>
-    <t>Canela y clavo, anÍ­s y manzanilla</t>
-  </si>
-  <si>
-    <t>Guarnición adicional</t>
-  </si>
-  <si>
-    <t>Acompañamiento crujiente</t>
-  </si>
-  <si>
     <t>PORCIÓN DE PAPAS FRITAS</t>
   </si>
   <si>
@@ -703,9 +592,6 @@
     <t>ENROLLADO DE POLLO CONPIÑA Y DURAZNO</t>
   </si>
   <si>
-    <t>PATO CONPIÑA</t>
-  </si>
-  <si>
     <t>PATO CONPIÑA Y DURAZNO</t>
   </si>
   <si>
@@ -718,33 +604,18 @@
     <t>ALITAS EN SALSAOSTIÓN</t>
   </si>
   <si>
-    <t>Arroz chaufa clásico</t>
-  </si>
-  <si>
     <t>CHAUFA DE POLLO CON CHAMPIÑONES</t>
   </si>
   <si>
     <t>Porción grande para compartir</t>
   </si>
   <si>
-    <t>Porción grande especial</t>
-  </si>
-  <si>
-    <t>Pollo crujiente en salsa de limón</t>
-  </si>
-  <si>
     <t>Incluye Chaufa, Plátano y Ensalada</t>
   </si>
   <si>
     <t>AEROPUERTO DE POLLO CON CHAMPIÑONES</t>
   </si>
   <si>
-    <t>Combinación clásica de chaufa y tallarín</t>
-  </si>
-  <si>
-    <t>Chaufa y tallarín saltado</t>
-  </si>
-  <si>
     <t>TALLARIN SALTADO DE POLLO CON CHAMPIÑONES</t>
   </si>
   <si>
@@ -764,6 +635,18 @@
   </si>
   <si>
     <t>PLATOS DULCES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incluye Chaufa + Papas </t>
+  </si>
+  <si>
+    <t>Canela y clavo, anis y manzanilla</t>
+  </si>
+  <si>
+    <t>PATO CON CHAMPIÑONES</t>
+  </si>
+  <si>
+    <t>PATO CON PIÑA</t>
   </si>
 </sst>
 </file>
@@ -1672,7 +1555,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="D4">
         <v>37</v>
@@ -1689,7 +1572,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="D5">
         <v>35</v>
@@ -1703,16 +1586,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>205</v>
       </c>
       <c r="D6">
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1723,13 +1606,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>205</v>
       </c>
       <c r="D7">
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1737,16 +1620,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>205</v>
       </c>
       <c r="D8">
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1754,16 +1637,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>205</v>
       </c>
       <c r="D9">
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1771,16 +1654,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="D10">
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1788,16 +1671,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="D11">
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1805,16 +1688,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D12">
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1822,16 +1702,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D13">
         <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1839,16 +1716,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>223</v>
-      </c>
-      <c r="C14" t="s">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="D14">
         <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1856,16 +1730,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>231</v>
-      </c>
-      <c r="C15" t="s">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="D15">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1873,16 +1744,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16">
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1890,16 +1758,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" t="s">
         <v>21</v>
       </c>
       <c r="D17">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1907,16 +1772,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>230</v>
-      </c>
-      <c r="C18" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="D18">
         <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1924,16 +1786,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="D19">
         <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1941,16 +1803,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>210</v>
-      </c>
-      <c r="C20" t="s">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="D20">
         <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1958,16 +1817,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="D21">
         <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1975,16 +1834,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="D22">
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1992,16 +1851,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D23">
         <v>17</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -2009,16 +1865,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -2026,16 +1879,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -2043,16 +1893,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" t="s">
         <v>30</v>
       </c>
       <c r="D26">
         <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -2060,16 +1907,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D27">
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -2077,16 +1921,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D28">
         <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -2094,16 +1935,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D29">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -2111,16 +1949,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D30">
         <v>19</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -2128,16 +1963,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D31">
         <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -2145,16 +1977,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D32">
         <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -2162,16 +1991,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D33">
         <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2179,16 +2005,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D34">
         <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2196,16 +2019,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D35">
         <v>29</v>
       </c>
       <c r="E35" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2213,16 +2033,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" t="s">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="D36">
         <v>17</v>
       </c>
       <c r="E36" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2230,16 +2047,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" t="s">
-        <v>232</v>
+        <v>42</v>
       </c>
       <c r="D37">
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2247,16 +2061,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" t="s">
-        <v>232</v>
+        <v>43</v>
       </c>
       <c r="D38">
         <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2264,16 +2075,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" t="s">
-        <v>232</v>
+        <v>44</v>
       </c>
       <c r="D39">
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2281,16 +2089,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
-      </c>
-      <c r="C40" t="s">
-        <v>232</v>
+        <v>45</v>
       </c>
       <c r="D40">
         <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2298,16 +2103,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" t="s">
-        <v>232</v>
+        <v>46</v>
       </c>
       <c r="D41">
         <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2315,16 +2117,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" t="s">
-        <v>232</v>
+        <v>47</v>
       </c>
       <c r="D42">
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2332,16 +2131,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
-      </c>
-      <c r="C43" t="s">
-        <v>232</v>
+        <v>48</v>
       </c>
       <c r="D43">
         <v>27</v>
       </c>
       <c r="E43" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2349,16 +2145,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" t="s">
-        <v>232</v>
+        <v>49</v>
       </c>
       <c r="D44">
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -2366,16 +2159,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" t="s">
-        <v>232</v>
+        <v>50</v>
       </c>
       <c r="D45">
         <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2383,16 +2173,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" t="s">
-        <v>232</v>
+        <v>51</v>
       </c>
       <c r="D46">
         <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2400,16 +2187,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
-      </c>
-      <c r="C47" t="s">
-        <v>232</v>
+        <v>52</v>
       </c>
       <c r="D47">
         <v>32</v>
       </c>
       <c r="E47" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2417,16 +2201,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" t="s">
-        <v>232</v>
+        <v>53</v>
       </c>
       <c r="D48">
         <v>27</v>
       </c>
       <c r="E48" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -2434,16 +2215,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>233</v>
-      </c>
-      <c r="C49" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="D49">
         <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -2451,16 +2229,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D50">
         <v>27</v>
       </c>
       <c r="E50" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -2468,16 +2243,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" t="s">
-        <v>232</v>
+        <v>55</v>
       </c>
       <c r="D51">
         <v>27</v>
       </c>
       <c r="E51" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -2485,16 +2257,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
-      </c>
-      <c r="C52" t="s">
-        <v>232</v>
+        <v>56</v>
       </c>
       <c r="D52">
         <v>32</v>
       </c>
       <c r="E52" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -2502,16 +2271,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D53">
         <v>36</v>
       </c>
       <c r="E53" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -2519,16 +2288,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="D54">
         <v>51</v>
       </c>
       <c r="E54" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -2536,16 +2305,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
-      </c>
-      <c r="C55" t="s">
-        <v>235</v>
+        <v>60</v>
       </c>
       <c r="D55">
         <v>69</v>
       </c>
       <c r="E55" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -2553,16 +2319,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
-      </c>
-      <c r="C56" t="s">
-        <v>239</v>
+        <v>61</v>
       </c>
       <c r="D56">
         <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -2570,16 +2333,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
-      </c>
-      <c r="C57" t="s">
-        <v>239</v>
+        <v>63</v>
       </c>
       <c r="D57">
         <v>22</v>
       </c>
       <c r="E57" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -2587,16 +2347,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
-      </c>
-      <c r="C58" t="s">
-        <v>239</v>
+        <v>64</v>
       </c>
       <c r="D58">
         <v>22</v>
       </c>
       <c r="E58" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -2604,16 +2361,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
-      </c>
-      <c r="C59" t="s">
-        <v>239</v>
+        <v>65</v>
       </c>
       <c r="D59">
         <v>22</v>
       </c>
       <c r="E59" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -2621,16 +2375,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>209</v>
-      </c>
-      <c r="C60" t="s">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="D60">
         <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -2638,16 +2389,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" t="s">
-        <v>239</v>
+        <v>66</v>
       </c>
       <c r="D61">
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -2655,16 +2403,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
-      </c>
-      <c r="C62" t="s">
-        <v>239</v>
+        <v>67</v>
       </c>
       <c r="D62">
         <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -2672,16 +2417,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>238</v>
-      </c>
-      <c r="C63" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="D63">
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -2689,16 +2431,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
-      </c>
-      <c r="C64" t="s">
-        <v>239</v>
+        <v>68</v>
       </c>
       <c r="D64">
         <v>30</v>
       </c>
       <c r="E64" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -2706,16 +2445,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
-      </c>
-      <c r="C65" t="s">
-        <v>239</v>
+        <v>69</v>
       </c>
       <c r="D65">
         <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -2723,16 +2459,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
-      </c>
-      <c r="C66" t="s">
-        <v>239</v>
+        <v>70</v>
       </c>
       <c r="D66">
         <v>28</v>
       </c>
       <c r="E66" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -2740,16 +2473,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
-      </c>
-      <c r="C67" t="s">
-        <v>239</v>
+        <v>71</v>
       </c>
       <c r="D67">
         <v>28</v>
       </c>
       <c r="E67" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -2757,16 +2487,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
-      </c>
-      <c r="C68" t="s">
-        <v>239</v>
+        <v>72</v>
       </c>
       <c r="D68">
         <v>33</v>
       </c>
       <c r="E68" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -2774,16 +2501,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
-      </c>
-      <c r="C69" t="s">
-        <v>240</v>
+        <v>73</v>
       </c>
       <c r="D69">
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2791,16 +2515,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
-      </c>
-      <c r="C70" t="s">
-        <v>240</v>
+        <v>75</v>
       </c>
       <c r="D70">
         <v>22</v>
       </c>
       <c r="E70" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2808,16 +2529,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>80</v>
-      </c>
-      <c r="C71" t="s">
-        <v>240</v>
+        <v>76</v>
       </c>
       <c r="D71">
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -2825,16 +2543,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
-      </c>
-      <c r="C72" t="s">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="D72">
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -2842,16 +2557,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
-      </c>
-      <c r="C73" t="s">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="D73">
         <v>22</v>
       </c>
       <c r="E73" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -2859,16 +2571,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" t="s">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="D74">
         <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -2876,16 +2585,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
-      </c>
-      <c r="C75" t="s">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="D75">
         <v>25</v>
       </c>
       <c r="E75" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -2893,16 +2599,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
-      </c>
-      <c r="C76" t="s">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="D76">
         <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2910,16 +2613,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
-      </c>
-      <c r="C77" t="s">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="D77">
         <v>22</v>
       </c>
       <c r="E77" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2927,16 +2627,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
-      </c>
-      <c r="C78" t="s">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="D78">
         <v>30</v>
       </c>
       <c r="E78" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2944,16 +2641,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" t="s">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="D79">
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -2961,16 +2655,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>89</v>
-      </c>
-      <c r="C80" t="s">
-        <v>240</v>
+        <v>85</v>
       </c>
       <c r="D80">
         <v>31</v>
       </c>
       <c r="E80" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2978,16 +2669,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
-      </c>
-      <c r="C81" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D81">
         <v>22</v>
       </c>
       <c r="E81" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2995,16 +2683,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
-      </c>
-      <c r="C82" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D82">
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -3012,16 +2697,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>94</v>
-      </c>
-      <c r="C83" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D83">
         <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -3029,16 +2711,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>95</v>
-      </c>
-      <c r="C84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D84">
         <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -3046,16 +2725,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
-      </c>
-      <c r="C85" t="s">
         <v>91</v>
       </c>
       <c r="D85">
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -3063,16 +2739,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>97</v>
-      </c>
-      <c r="C86" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D86">
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -3080,16 +2753,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
-      </c>
-      <c r="C87" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D87">
         <v>22</v>
       </c>
       <c r="E87" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -3097,16 +2767,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>101</v>
-      </c>
-      <c r="C88" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D88">
         <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -3114,16 +2781,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>102</v>
-      </c>
-      <c r="C89" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D89">
         <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -3131,16 +2795,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>103</v>
-      </c>
-      <c r="C90" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D90">
         <v>27</v>
       </c>
       <c r="E90" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -3148,16 +2809,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>104</v>
-      </c>
-      <c r="C91" t="s">
         <v>98</v>
       </c>
       <c r="D91">
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -3165,16 +2823,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>105</v>
-      </c>
-      <c r="C92" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D92">
         <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -3182,16 +2837,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
-      </c>
-      <c r="C93" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D93">
         <v>29</v>
       </c>
       <c r="E93" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -3199,16 +2851,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>241</v>
-      </c>
-      <c r="C94" t="s">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="D94">
         <v>25</v>
       </c>
       <c r="E94" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -3216,16 +2865,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
-      </c>
-      <c r="C95" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D95">
         <v>29</v>
       </c>
       <c r="E95" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -3233,16 +2879,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
-      </c>
-      <c r="C96" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D96">
         <v>22</v>
       </c>
       <c r="E96" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -3250,16 +2893,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>110</v>
-      </c>
-      <c r="C97" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D97">
         <v>30</v>
       </c>
       <c r="E97" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -3267,16 +2907,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>111</v>
-      </c>
-      <c r="C98" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D98">
         <v>26</v>
       </c>
       <c r="E98" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -3284,16 +2921,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>113</v>
-      </c>
-      <c r="C99" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D99">
         <v>38</v>
       </c>
       <c r="E99" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -3301,16 +2935,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>114</v>
-      </c>
-      <c r="C100" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D100">
         <v>20</v>
       </c>
       <c r="E100" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -3318,16 +2949,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>117</v>
-      </c>
-      <c r="C101" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D101">
         <v>22</v>
       </c>
       <c r="E101" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -3335,16 +2963,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>118</v>
-      </c>
-      <c r="C102" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D102">
         <v>29</v>
       </c>
       <c r="E102" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -3352,16 +2977,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>246</v>
-      </c>
-      <c r="C103" t="s">
-        <v>115</v>
+        <v>203</v>
       </c>
       <c r="D103">
         <v>25</v>
       </c>
       <c r="E103" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -3369,16 +2991,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>119</v>
-      </c>
-      <c r="C104" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D104">
         <v>26</v>
       </c>
       <c r="E104" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -3386,16 +3005,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>120</v>
-      </c>
-      <c r="C105" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D105">
         <v>24</v>
       </c>
       <c r="E105" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -3403,16 +3019,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>121</v>
-      </c>
-      <c r="C106" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D106">
         <v>26</v>
       </c>
       <c r="E106" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -3420,16 +3033,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>123</v>
-      </c>
-      <c r="C107" t="s">
-        <v>236</v>
+        <v>113</v>
       </c>
       <c r="D107">
         <v>27</v>
       </c>
       <c r="E107" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -3437,16 +3047,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>124</v>
-      </c>
-      <c r="C108" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D108">
         <v>22</v>
       </c>
       <c r="E108" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -3454,16 +3061,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>224</v>
-      </c>
-      <c r="C109" t="s">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="D109">
         <v>22</v>
       </c>
       <c r="E109" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -3471,16 +3075,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>126</v>
-      </c>
-      <c r="C110" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D110">
         <v>22</v>
       </c>
       <c r="E110" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -3488,16 +3089,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>127</v>
-      </c>
-      <c r="C111" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D111">
         <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -3505,16 +3103,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>128</v>
-      </c>
-      <c r="C112" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D112">
         <v>27</v>
       </c>
       <c r="E112" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -3522,16 +3117,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>130</v>
-      </c>
-      <c r="C113" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D113">
         <v>27</v>
       </c>
       <c r="E113" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -3539,16 +3131,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>132</v>
-      </c>
-      <c r="C114" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D114">
         <v>20</v>
       </c>
       <c r="E114" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -3556,16 +3145,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>135</v>
-      </c>
-      <c r="C115" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D115">
         <v>20</v>
       </c>
       <c r="E115" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -3573,16 +3159,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>136</v>
-      </c>
-      <c r="C116" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D116">
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -3590,16 +3173,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>137</v>
-      </c>
-      <c r="C117" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D117">
         <v>29</v>
       </c>
       <c r="E117" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -3607,16 +3187,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>138</v>
-      </c>
-      <c r="C118" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D118">
         <v>30</v>
       </c>
       <c r="E118" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -3624,16 +3201,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>139</v>
-      </c>
-      <c r="C119" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D119">
         <v>28</v>
       </c>
       <c r="E119" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -3641,16 +3215,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>142</v>
-      </c>
-      <c r="C120" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="D120">
         <v>28</v>
       </c>
       <c r="E120" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -3658,16 +3229,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>143</v>
-      </c>
-      <c r="C121" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D121">
         <v>28</v>
       </c>
       <c r="E121" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -3675,16 +3243,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>225</v>
-      </c>
-      <c r="C122" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="D122">
         <v>28</v>
       </c>
       <c r="E122" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -3692,16 +3257,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>144</v>
-      </c>
-      <c r="C123" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D123">
         <v>28</v>
       </c>
       <c r="E123" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -3709,16 +3271,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>145</v>
-      </c>
-      <c r="C124" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D124">
         <v>28</v>
       </c>
       <c r="E124" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -3726,16 +3285,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>146</v>
-      </c>
-      <c r="C125" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D125">
         <v>30</v>
       </c>
       <c r="E125" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -3743,16 +3299,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>226</v>
-      </c>
-      <c r="C126" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="D126">
         <v>32</v>
       </c>
       <c r="E126" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
@@ -3760,16 +3313,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>147</v>
-      </c>
-      <c r="C127" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D127">
         <v>32</v>
       </c>
       <c r="E127" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -3777,16 +3327,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>148</v>
-      </c>
-      <c r="C128" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="D128">
         <v>38</v>
       </c>
       <c r="E128" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -3794,16 +3341,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>150</v>
-      </c>
-      <c r="C129" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="D129">
         <v>39</v>
       </c>
       <c r="E129" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -3811,16 +3355,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>152</v>
-      </c>
-      <c r="C130" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D130">
         <v>38</v>
       </c>
       <c r="E130" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -3828,16 +3369,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>154</v>
-      </c>
-      <c r="C131" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="D131">
         <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -3845,16 +3383,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>157</v>
-      </c>
-      <c r="C132" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="D132">
         <v>24</v>
       </c>
       <c r="E132" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -3862,16 +3397,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>242</v>
-      </c>
-      <c r="C133" t="s">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="D133">
         <v>26</v>
       </c>
       <c r="E133" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -3879,16 +3411,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>158</v>
-      </c>
-      <c r="C134" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="D134">
         <v>30</v>
       </c>
       <c r="E134" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -3896,16 +3425,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>161</v>
-      </c>
-      <c r="C135" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="D135">
         <v>32</v>
       </c>
       <c r="E135" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -3913,16 +3439,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>162</v>
-      </c>
-      <c r="C136" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D136">
         <v>38</v>
       </c>
       <c r="E136" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -3930,16 +3453,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>164</v>
-      </c>
-      <c r="C137" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="D137">
         <v>30</v>
       </c>
       <c r="E137" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -3947,16 +3467,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>167</v>
-      </c>
-      <c r="C138" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="D138">
         <v>30</v>
       </c>
       <c r="E138" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
@@ -3964,16 +3481,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>168</v>
-      </c>
-      <c r="C139" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="D139">
         <v>30</v>
       </c>
       <c r="E139" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -3981,16 +3495,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>169</v>
-      </c>
-      <c r="C140" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D140">
         <v>30</v>
       </c>
       <c r="E140" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
@@ -3998,16 +3509,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>227</v>
-      </c>
-      <c r="C141" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="D141">
         <v>30</v>
       </c>
       <c r="E141" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -4015,16 +3523,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>170</v>
-      </c>
-      <c r="C142" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="D142">
         <v>30</v>
       </c>
       <c r="E142" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -4032,16 +3537,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>228</v>
-      </c>
-      <c r="C143" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="D143">
         <v>32</v>
       </c>
       <c r="E143" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -4049,16 +3551,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>171</v>
-      </c>
-      <c r="C144" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="D144">
         <v>26</v>
       </c>
       <c r="E144" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
@@ -4066,16 +3565,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>174</v>
-      </c>
-      <c r="C145" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="D145">
         <v>32</v>
       </c>
       <c r="E145" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
@@ -4083,16 +3579,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>175</v>
-      </c>
-      <c r="C146" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="D146">
         <v>22</v>
       </c>
       <c r="E146" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
@@ -4100,16 +3593,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>178</v>
-      </c>
-      <c r="C147" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="D147">
         <v>24</v>
       </c>
       <c r="E147" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
@@ -4117,16 +3607,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>179</v>
-      </c>
-      <c r="C148" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="D148">
         <v>27</v>
       </c>
       <c r="E148" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
@@ -4134,16 +3621,16 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="C149" t="s">
-        <v>237</v>
+        <v>196</v>
       </c>
       <c r="D149">
         <v>33</v>
       </c>
       <c r="E149" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
@@ -4151,16 +3638,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>182</v>
-      </c>
-      <c r="C150" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="D150">
         <v>33</v>
       </c>
       <c r="E150" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
@@ -4168,16 +3652,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>219</v>
-      </c>
-      <c r="C151" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="D151">
         <v>12</v>
       </c>
       <c r="E151" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
@@ -4185,16 +3666,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>220</v>
-      </c>
-      <c r="C152" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="D152">
         <v>7</v>
       </c>
       <c r="E152" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
@@ -4202,16 +3680,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>221</v>
-      </c>
-      <c r="C153" t="s">
-        <v>214</v>
+        <v>184</v>
       </c>
       <c r="D153">
         <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
@@ -4219,16 +3694,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>185</v>
-      </c>
-      <c r="C154" t="s">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="D154">
         <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
@@ -4236,16 +3708,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>186</v>
-      </c>
-      <c r="C155" t="s">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="D155">
         <v>5</v>
       </c>
       <c r="E155" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
@@ -4253,16 +3722,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>216</v>
-      </c>
-      <c r="C156" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="D156">
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
@@ -4270,16 +3736,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>217</v>
-      </c>
-      <c r="C157" t="s">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="D157">
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
@@ -4287,16 +3750,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>218</v>
-      </c>
-      <c r="C158" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="D158">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
@@ -4304,16 +3764,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>187</v>
-      </c>
-      <c r="C159" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="D159">
         <v>3</v>
       </c>
       <c r="E159" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
@@ -4321,16 +3778,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>189</v>
-      </c>
-      <c r="C160" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="D160">
         <v>13</v>
       </c>
       <c r="E160" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
@@ -4338,16 +3792,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>245</v>
-      </c>
-      <c r="C161" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="D161">
         <v>11</v>
       </c>
       <c r="E161" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
@@ -4355,16 +3806,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>191</v>
-      </c>
-      <c r="C162" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="D162">
         <v>7</v>
       </c>
       <c r="E162" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
@@ -4372,16 +3820,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>244</v>
-      </c>
-      <c r="C163" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D163">
         <v>6</v>
       </c>
       <c r="E163" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
@@ -4389,16 +3834,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>192</v>
-      </c>
-      <c r="C164" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="D164">
         <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
@@ -4406,16 +3848,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>194</v>
-      </c>
-      <c r="C165" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="D165">
         <v>6</v>
       </c>
       <c r="E165" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
@@ -4423,16 +3862,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>196</v>
-      </c>
-      <c r="C166" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D166">
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
@@ -4440,16 +3876,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>198</v>
-      </c>
-      <c r="C167" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="D167">
         <v>15</v>
       </c>
       <c r="E167" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
@@ -4457,16 +3890,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>200</v>
-      </c>
-      <c r="C168" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="D168">
         <v>17</v>
       </c>
       <c r="E168" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
@@ -4474,16 +3904,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>202</v>
-      </c>
-      <c r="C169" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="D169">
         <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
@@ -4491,16 +3918,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="C170" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D170">
         <v>4</v>
       </c>
       <c r="E170" t="s">
-        <v>205</v>
+        <v>171</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
@@ -4508,16 +3935,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="C171" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
       <c r="D171">
         <v>5</v>
       </c>
       <c r="E171" t="s">
-        <v>205</v>
+        <v>171</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
@@ -4525,16 +3952,16 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="C172" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="D172">
         <v>26</v>
       </c>
       <c r="E172" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Catalogo_Productos.xlsx
+++ b/Catalogo_Productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bonny Rodriguez\Desktop\App_chifa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038251D7-F34B-4972-B590-5DC69987A81C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13941B6A-024F-4FEA-9825-F92D942AC7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7701F3F5-2ED2-4A4E-974A-8765CB3D8F1F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="249">
   <si>
     <t>ID</t>
   </si>
@@ -61,6 +61,9 @@
     <t>ALITAS REBOZADAS 4 PZS</t>
   </si>
   <si>
+    <t>Incluye Chaufa + Papas + Vinagreta</t>
+  </si>
+  <si>
     <t>ALITAS REBOZADAS</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>ALITAS EN SALSA BBQ</t>
   </si>
   <si>
+    <t>Incluye Chaufa + Papas + Ensalada</t>
+  </si>
+  <si>
     <t>ALITAS ESPECIALES</t>
   </si>
   <si>
@@ -79,6 +85,9 @@
     <t>ALITAS CON VERDURAS</t>
   </si>
   <si>
+    <t>Alitas especiales de la casa</t>
+  </si>
+  <si>
     <t>ALITAS CON TAMARINDO</t>
   </si>
   <si>
@@ -103,6 +112,9 @@
     <t>SOPA WANTAN DE POLLO</t>
   </si>
   <si>
+    <t>Sopa caliente tradicional</t>
+  </si>
+  <si>
     <t>SOPAS</t>
   </si>
   <si>
@@ -283,6 +295,9 @@
     <t>LOMO SALTADO DE POLLO</t>
   </si>
   <si>
+    <t>Saltado jugoso tradicional</t>
+  </si>
+  <si>
     <t>LOMOS SALTADOS</t>
   </si>
   <si>
@@ -301,6 +316,9 @@
     <t>TALLARIN SALTADO DE POLLO</t>
   </si>
   <si>
+    <t>Fideos saltados al wok</t>
+  </si>
+  <si>
     <t>TALLARINES SALTADOS</t>
   </si>
   <si>
@@ -331,18 +349,27 @@
     <t>TALLARIN FRITO DE POLLO</t>
   </si>
   <si>
+    <t>Fideos fritos estilo chifa</t>
+  </si>
+  <si>
     <t>TALLARIN FRITO ESPECIAL</t>
   </si>
   <si>
     <t>TALLARIN EN TROZOS CON VERDURA</t>
   </si>
   <si>
+    <t>Fideos estilo chifa</t>
+  </si>
+  <si>
     <t>TALLARIN TAYPA</t>
   </si>
   <si>
     <t>POLLO CON VERDURAS + CHAUFA</t>
   </si>
   <si>
+    <t>Platos salados tradicionales</t>
+  </si>
+  <si>
     <t>PLATOS SALADOS</t>
   </si>
   <si>
@@ -361,12 +388,18 @@
     <t>CHI JAU KAY + CHAUFA</t>
   </si>
   <si>
+    <t>Pollo crujiente en salsa salada</t>
+  </si>
+  <si>
     <t>LIMON KAY + CHAUFA</t>
   </si>
   <si>
     <t>POLLO CON TAMARINDO + CHAUFA</t>
   </si>
   <si>
+    <t>Platos agridulces tradicionales</t>
+  </si>
+  <si>
     <t>POLLO CON DURAZNO + CHAUFA</t>
   </si>
   <si>
@@ -376,12 +409,21 @@
     <t>KAM LU WANTAN + CHAUFA</t>
   </si>
   <si>
+    <t>Wantanes fritos con salsa agridulce y carnes</t>
+  </si>
+  <si>
     <t>TIPA KAY + CHAUFA</t>
   </si>
   <si>
+    <t>Pollo crujiente en salsa agridulce</t>
+  </si>
+  <si>
     <t>TORTILLA DE POLLO</t>
   </si>
   <si>
+    <t>Tortilla al estilo chifa</t>
+  </si>
+  <si>
     <t>TORTILLAS</t>
   </si>
   <si>
@@ -400,6 +442,9 @@
     <t>ENROLLADO DE POLLO CON OSTION</t>
   </si>
   <si>
+    <t>Enrollados sabrosos de la casa</t>
+  </si>
+  <si>
     <t>ENROLLADOS</t>
   </si>
   <si>
@@ -424,15 +469,27 @@
     <t>TAYPA</t>
   </si>
   <si>
+    <t>Especialidad taypa de la casa</t>
+  </si>
+  <si>
     <t>TAYPA A LA PLANCHA</t>
   </si>
   <si>
+    <t>Especialidad taypa caliente</t>
+  </si>
+  <si>
     <t>TAYPA DE LANGOSTINOS</t>
   </si>
   <si>
+    <t>Especialidad taypa marina</t>
+  </si>
+  <si>
     <t>RES CON VERDURA</t>
   </si>
   <si>
+    <t>Platos a base de carne de res</t>
+  </si>
+  <si>
     <t>RES</t>
   </si>
   <si>
@@ -442,6 +499,9 @@
     <t>LANGOSTINOS CON VERDURA</t>
   </si>
   <si>
+    <t>Platos marinos al wok</t>
+  </si>
+  <si>
     <t>LANGOSTINOS</t>
   </si>
   <si>
@@ -451,9 +511,15 @@
     <t>LANGOSTINOS A LA PLANCHA</t>
   </si>
   <si>
+    <t>Platos marinos calientes</t>
+  </si>
+  <si>
     <t>PATO CON VERDURA</t>
   </si>
   <si>
+    <t>Platos especiales de pato</t>
+  </si>
+  <si>
     <t>PATO</t>
   </si>
   <si>
@@ -466,9 +532,15 @@
     <t>PATO AGRIDULCE</t>
   </si>
   <si>
+    <t>PATO CON CHAMPIÃ‘ONES</t>
+  </si>
+  <si>
     <t>CHICHARRON DE POLLO</t>
   </si>
   <si>
+    <t>Crujiente y dorado</t>
+  </si>
+  <si>
     <t>CHICHARRONES</t>
   </si>
   <si>
@@ -478,6 +550,9 @@
     <t>CHANCHO CON TAMARINDO</t>
   </si>
   <si>
+    <t>Platos a base de carne de cerdo</t>
+  </si>
+  <si>
     <t>CHANCHO</t>
   </si>
   <si>
@@ -496,6 +571,9 @@
     <t>COSTILLA EN SALSA BBQ</t>
   </si>
   <si>
+    <t>Costillas sabrosas de la casa</t>
+  </si>
+  <si>
     <t>PORCIONES</t>
   </si>
   <si>
@@ -508,30 +586,54 @@
     <t>HUEVO</t>
   </si>
   <si>
+    <t>Adicional</t>
+  </si>
+  <si>
     <t>JARRA CHICHA MORADA</t>
   </si>
   <si>
+    <t>Bebida refrescante tradicional</t>
+  </si>
+  <si>
     <t>1/2 CHICHA MORADA</t>
   </si>
   <si>
     <t>INKA/COCA DESCARTABLE PERSONAL</t>
   </si>
   <si>
+    <t>Gaseosa individual</t>
+  </si>
+  <si>
     <t>INCA COLA GORDITA</t>
   </si>
   <si>
+    <t>Gaseosa familiar mediana</t>
+  </si>
+  <si>
     <t>INCA/COCA 1 LTS</t>
   </si>
   <si>
+    <t>Gaseosa familiar</t>
+  </si>
+  <si>
     <t>INCA/COCA 2.5 LTS</t>
   </si>
   <si>
+    <t>Gaseosa familiar grande</t>
+  </si>
+  <si>
     <t>INCA/COCA 3 LTS</t>
   </si>
   <si>
+    <t>Gaseosa familiar gigante</t>
+  </si>
+  <si>
     <t>CERVEZA</t>
   </si>
   <si>
+    <t>Bebida helada</t>
+  </si>
+  <si>
     <t>TE</t>
   </si>
   <si>
@@ -559,6 +661,15 @@
     <t>BEBIDAS FRÍAS</t>
   </si>
   <si>
+    <t>Canela y clavo, anÍ­s y manzanilla</t>
+  </si>
+  <si>
+    <t>Guarnición adicional</t>
+  </si>
+  <si>
+    <t>Acompañamiento crujiente</t>
+  </si>
+  <si>
     <t>PORCIÓN DE PAPAS FRITAS</t>
   </si>
   <si>
@@ -592,6 +703,9 @@
     <t>ENROLLADO DE POLLO CONPIÑA Y DURAZNO</t>
   </si>
   <si>
+    <t>PATO CONPIÑA</t>
+  </si>
+  <si>
     <t>PATO CONPIÑA Y DURAZNO</t>
   </si>
   <si>
@@ -604,18 +718,33 @@
     <t>ALITAS EN SALSAOSTIÓN</t>
   </si>
   <si>
+    <t>Arroz chaufa clásico</t>
+  </si>
+  <si>
     <t>CHAUFA DE POLLO CON CHAMPIÑONES</t>
   </si>
   <si>
     <t>Porción grande para compartir</t>
   </si>
   <si>
+    <t>Porción grande especial</t>
+  </si>
+  <si>
+    <t>Pollo crujiente en salsa de limón</t>
+  </si>
+  <si>
     <t>Incluye Chaufa, Plátano y Ensalada</t>
   </si>
   <si>
     <t>AEROPUERTO DE POLLO CON CHAMPIÑONES</t>
   </si>
   <si>
+    <t>Combinación clásica de chaufa y tallarín</t>
+  </si>
+  <si>
+    <t>Chaufa y tallarín saltado</t>
+  </si>
+  <si>
     <t>TALLARIN SALTADO DE POLLO CON CHAMPIÑONES</t>
   </si>
   <si>
@@ -638,15 +767,6 @@
   </si>
   <si>
     <t xml:space="preserve">Incluye Chaufa + Papas </t>
-  </si>
-  <si>
-    <t>Canela y clavo, anis y manzanilla</t>
-  </si>
-  <si>
-    <t>PATO CON CHAMPIÑONES</t>
-  </si>
-  <si>
-    <t>PATO CON PIÑA</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1675,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="D4">
         <v>37</v>
@@ -1572,7 +1692,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="D5">
         <v>35</v>
@@ -1586,16 +1706,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1606,13 +1726,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="D7">
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1620,16 +1740,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="D8">
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1637,16 +1757,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="D9">
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1654,16 +1774,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="D10">
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1671,16 +1791,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="D11">
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1688,13 +1808,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
       </c>
       <c r="D12">
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1702,13 +1825,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
       </c>
       <c r="D13">
         <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1716,13 +1842,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>186</v>
+        <v>223</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
       </c>
       <c r="D14">
         <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1730,13 +1859,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>231</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
       </c>
       <c r="D15">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1744,13 +1876,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
       </c>
       <c r="D16">
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1758,13 +1893,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
         <v>21</v>
       </c>
       <c r="D17">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1772,13 +1910,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>192</v>
+        <v>230</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
       </c>
       <c r="D18">
         <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1786,16 +1927,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c r="D19">
         <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1803,13 +1944,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>176</v>
+        <v>210</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
       </c>
       <c r="D20">
         <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1817,16 +1961,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c r="D21">
         <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1834,16 +1978,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c r="D22">
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1851,13 +1995,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
       </c>
       <c r="D23">
         <v>17</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1865,13 +2012,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
       </c>
       <c r="D24">
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1879,13 +2029,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
       </c>
       <c r="D25">
         <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1893,13 +2046,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
         <v>30</v>
       </c>
       <c r="D26">
         <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1907,13 +2063,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
       </c>
       <c r="D27">
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1921,13 +2080,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
       </c>
       <c r="D28">
         <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1935,13 +2097,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
       </c>
       <c r="D29">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1949,13 +2114,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
       </c>
       <c r="D30">
         <v>19</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1963,13 +2131,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>30</v>
       </c>
       <c r="D31">
         <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1977,13 +2148,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
       </c>
       <c r="D32">
         <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1991,13 +2165,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="C33" t="s">
+        <v>30</v>
       </c>
       <c r="D33">
         <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2005,13 +2182,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>42</v>
+      </c>
+      <c r="C34" t="s">
+        <v>30</v>
       </c>
       <c r="D34">
         <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2019,13 +2199,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>43</v>
+      </c>
+      <c r="C35" t="s">
+        <v>30</v>
       </c>
       <c r="D35">
         <v>29</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2033,13 +2216,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>44</v>
+      </c>
+      <c r="C36" t="s">
+        <v>232</v>
       </c>
       <c r="D36">
         <v>17</v>
       </c>
       <c r="E36" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2047,13 +2233,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="C37" t="s">
+        <v>232</v>
       </c>
       <c r="D37">
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2061,13 +2250,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="C38" t="s">
+        <v>232</v>
       </c>
       <c r="D38">
         <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2075,13 +2267,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="C39" t="s">
+        <v>232</v>
       </c>
       <c r="D39">
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2089,13 +2284,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>49</v>
+      </c>
+      <c r="C40" t="s">
+        <v>232</v>
       </c>
       <c r="D40">
         <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2103,13 +2301,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="C41" t="s">
+        <v>232</v>
       </c>
       <c r="D41">
         <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2117,13 +2318,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+      <c r="C42" t="s">
+        <v>232</v>
       </c>
       <c r="D42">
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2131,13 +2335,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>232</v>
       </c>
       <c r="D43">
         <v>27</v>
       </c>
       <c r="E43" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2145,13 +2352,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>53</v>
+      </c>
+      <c r="C44" t="s">
+        <v>232</v>
       </c>
       <c r="D44">
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -2159,13 +2369,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>54</v>
+      </c>
+      <c r="C45" t="s">
+        <v>232</v>
       </c>
       <c r="D45">
         <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2173,13 +2386,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>55</v>
+      </c>
+      <c r="C46" t="s">
+        <v>232</v>
       </c>
       <c r="D46">
         <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2187,13 +2403,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>56</v>
+      </c>
+      <c r="C47" t="s">
+        <v>232</v>
       </c>
       <c r="D47">
         <v>32</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2201,13 +2420,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>232</v>
       </c>
       <c r="D48">
         <v>27</v>
       </c>
       <c r="E48" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -2215,13 +2437,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>194</v>
+        <v>233</v>
+      </c>
+      <c r="C49" t="s">
+        <v>232</v>
       </c>
       <c r="D49">
         <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -2229,13 +2454,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>58</v>
+      </c>
+      <c r="C50" t="s">
+        <v>232</v>
       </c>
       <c r="D50">
         <v>27</v>
       </c>
       <c r="E50" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -2243,13 +2471,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>59</v>
+      </c>
+      <c r="C51" t="s">
+        <v>232</v>
       </c>
       <c r="D51">
         <v>27</v>
       </c>
       <c r="E51" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -2257,13 +2488,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>60</v>
+      </c>
+      <c r="C52" t="s">
+        <v>232</v>
       </c>
       <c r="D52">
         <v>32</v>
       </c>
       <c r="E52" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -2271,16 +2505,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D53">
         <v>36</v>
       </c>
       <c r="E53" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -2288,16 +2522,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="D54">
         <v>51</v>
       </c>
       <c r="E54" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -2305,13 +2539,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="C55" t="s">
+        <v>235</v>
       </c>
       <c r="D55">
         <v>69</v>
       </c>
       <c r="E55" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -2319,13 +2556,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>61</v>
+        <v>65</v>
+      </c>
+      <c r="C56" t="s">
+        <v>239</v>
       </c>
       <c r="D56">
         <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -2333,13 +2573,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>67</v>
+      </c>
+      <c r="C57" t="s">
+        <v>239</v>
       </c>
       <c r="D57">
         <v>22</v>
       </c>
       <c r="E57" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -2347,13 +2590,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>68</v>
+      </c>
+      <c r="C58" t="s">
+        <v>239</v>
       </c>
       <c r="D58">
         <v>22</v>
       </c>
       <c r="E58" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -2361,13 +2607,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>65</v>
+        <v>69</v>
+      </c>
+      <c r="C59" t="s">
+        <v>239</v>
       </c>
       <c r="D59">
         <v>22</v>
       </c>
       <c r="E59" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -2375,13 +2624,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>175</v>
+        <v>209</v>
+      </c>
+      <c r="C60" t="s">
+        <v>239</v>
       </c>
       <c r="D60">
         <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -2389,13 +2641,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>70</v>
+      </c>
+      <c r="C61" t="s">
+        <v>239</v>
       </c>
       <c r="D61">
         <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -2403,13 +2658,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>71</v>
+      </c>
+      <c r="C62" t="s">
+        <v>239</v>
       </c>
       <c r="D62">
         <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -2417,13 +2675,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>197</v>
+        <v>238</v>
+      </c>
+      <c r="C63" t="s">
+        <v>239</v>
       </c>
       <c r="D63">
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -2431,13 +2692,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>72</v>
+      </c>
+      <c r="C64" t="s">
+        <v>239</v>
       </c>
       <c r="D64">
         <v>30</v>
       </c>
       <c r="E64" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -2445,13 +2709,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>73</v>
+      </c>
+      <c r="C65" t="s">
+        <v>239</v>
       </c>
       <c r="D65">
         <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -2459,13 +2726,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>74</v>
+      </c>
+      <c r="C66" t="s">
+        <v>239</v>
       </c>
       <c r="D66">
         <v>28</v>
       </c>
       <c r="E66" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -2473,13 +2743,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>75</v>
+      </c>
+      <c r="C67" t="s">
+        <v>239</v>
       </c>
       <c r="D67">
         <v>28</v>
       </c>
       <c r="E67" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -2487,13 +2760,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>76</v>
+      </c>
+      <c r="C68" t="s">
+        <v>239</v>
       </c>
       <c r="D68">
         <v>33</v>
       </c>
       <c r="E68" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -2501,13 +2777,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>73</v>
+        <v>77</v>
+      </c>
+      <c r="C69" t="s">
+        <v>240</v>
       </c>
       <c r="D69">
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2515,13 +2794,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>79</v>
+      </c>
+      <c r="C70" t="s">
+        <v>240</v>
       </c>
       <c r="D70">
         <v>22</v>
       </c>
       <c r="E70" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2529,13 +2811,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="C71" t="s">
+        <v>240</v>
       </c>
       <c r="D71">
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -2543,13 +2828,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>77</v>
+        <v>81</v>
+      </c>
+      <c r="C72" t="s">
+        <v>240</v>
       </c>
       <c r="D72">
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -2557,13 +2845,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>78</v>
+        <v>82</v>
+      </c>
+      <c r="C73" t="s">
+        <v>240</v>
       </c>
       <c r="D73">
         <v>22</v>
       </c>
       <c r="E73" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -2571,13 +2862,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>83</v>
+      </c>
+      <c r="C74" t="s">
+        <v>240</v>
       </c>
       <c r="D74">
         <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -2585,13 +2879,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>80</v>
+        <v>84</v>
+      </c>
+      <c r="C75" t="s">
+        <v>240</v>
       </c>
       <c r="D75">
         <v>25</v>
       </c>
       <c r="E75" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -2599,13 +2896,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>85</v>
+      </c>
+      <c r="C76" t="s">
+        <v>240</v>
       </c>
       <c r="D76">
         <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2613,13 +2913,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>82</v>
+        <v>86</v>
+      </c>
+      <c r="C77" t="s">
+        <v>240</v>
       </c>
       <c r="D77">
         <v>22</v>
       </c>
       <c r="E77" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2627,13 +2930,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>87</v>
+      </c>
+      <c r="C78" t="s">
+        <v>240</v>
       </c>
       <c r="D78">
         <v>30</v>
       </c>
       <c r="E78" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2641,13 +2947,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>88</v>
+      </c>
+      <c r="C79" t="s">
+        <v>240</v>
       </c>
       <c r="D79">
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -2655,13 +2964,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>89</v>
+      </c>
+      <c r="C80" t="s">
+        <v>240</v>
       </c>
       <c r="D80">
         <v>31</v>
       </c>
       <c r="E80" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2669,13 +2981,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="C81" t="s">
+        <v>91</v>
       </c>
       <c r="D81">
         <v>22</v>
       </c>
       <c r="E81" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2683,13 +2998,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>93</v>
+      </c>
+      <c r="C82" t="s">
+        <v>91</v>
       </c>
       <c r="D82">
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -2697,13 +3015,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>94</v>
+      </c>
+      <c r="C83" t="s">
+        <v>91</v>
       </c>
       <c r="D83">
         <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2711,13 +3032,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>90</v>
+        <v>95</v>
+      </c>
+      <c r="C84" t="s">
+        <v>91</v>
       </c>
       <c r="D84">
         <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2725,13 +3049,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C85" t="s">
         <v>91</v>
       </c>
       <c r="D85">
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -2739,13 +3066,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>97</v>
+      </c>
+      <c r="C86" t="s">
+        <v>98</v>
       </c>
       <c r="D86">
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2753,13 +3083,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="C87" t="s">
+        <v>98</v>
       </c>
       <c r="D87">
         <v>22</v>
       </c>
       <c r="E87" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -2767,13 +3100,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>95</v>
+        <v>101</v>
+      </c>
+      <c r="C88" t="s">
+        <v>98</v>
       </c>
       <c r="D88">
         <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -2781,13 +3117,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>96</v>
+        <v>102</v>
+      </c>
+      <c r="C89" t="s">
+        <v>98</v>
       </c>
       <c r="D89">
         <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -2795,13 +3134,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>97</v>
+        <v>103</v>
+      </c>
+      <c r="C90" t="s">
+        <v>98</v>
       </c>
       <c r="D90">
         <v>27</v>
       </c>
       <c r="E90" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2809,13 +3151,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>104</v>
+      </c>
+      <c r="C91" t="s">
         <v>98</v>
       </c>
       <c r="D91">
         <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -2823,13 +3168,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>99</v>
+        <v>105</v>
+      </c>
+      <c r="C92" t="s">
+        <v>98</v>
       </c>
       <c r="D92">
         <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -2837,13 +3185,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>100</v>
+        <v>106</v>
+      </c>
+      <c r="C93" t="s">
+        <v>98</v>
       </c>
       <c r="D93">
         <v>29</v>
       </c>
       <c r="E93" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -2851,13 +3202,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>198</v>
+        <v>241</v>
+      </c>
+      <c r="C94" t="s">
+        <v>98</v>
       </c>
       <c r="D94">
         <v>25</v>
       </c>
       <c r="E94" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -2865,13 +3219,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>101</v>
+        <v>107</v>
+      </c>
+      <c r="C95" t="s">
+        <v>98</v>
       </c>
       <c r="D95">
         <v>29</v>
       </c>
       <c r="E95" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -2879,13 +3236,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>102</v>
+        <v>108</v>
+      </c>
+      <c r="C96" t="s">
+        <v>109</v>
       </c>
       <c r="D96">
         <v>22</v>
       </c>
       <c r="E96" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -2893,13 +3253,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>103</v>
+        <v>110</v>
+      </c>
+      <c r="C97" t="s">
+        <v>109</v>
       </c>
       <c r="D97">
         <v>30</v>
       </c>
       <c r="E97" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -2907,13 +3270,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>104</v>
+        <v>111</v>
+      </c>
+      <c r="C98" t="s">
+        <v>112</v>
       </c>
       <c r="D98">
         <v>26</v>
       </c>
       <c r="E98" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -2921,13 +3287,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>105</v>
+        <v>113</v>
+      </c>
+      <c r="C99" t="s">
+        <v>112</v>
       </c>
       <c r="D99">
         <v>38</v>
       </c>
       <c r="E99" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -2935,13 +3304,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>106</v>
+        <v>114</v>
+      </c>
+      <c r="C100" t="s">
+        <v>115</v>
       </c>
       <c r="D100">
         <v>20</v>
       </c>
       <c r="E100" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -2949,13 +3321,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>108</v>
+        <v>117</v>
+      </c>
+      <c r="C101" t="s">
+        <v>115</v>
       </c>
       <c r="D101">
         <v>22</v>
       </c>
       <c r="E101" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -2963,13 +3338,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>109</v>
+        <v>118</v>
+      </c>
+      <c r="C102" t="s">
+        <v>115</v>
       </c>
       <c r="D102">
         <v>29</v>
       </c>
       <c r="E102" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -2977,13 +3355,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>203</v>
+        <v>246</v>
+      </c>
+      <c r="C103" t="s">
+        <v>115</v>
       </c>
       <c r="D103">
         <v>25</v>
       </c>
       <c r="E103" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -2991,13 +3372,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>110</v>
+        <v>119</v>
+      </c>
+      <c r="C104" t="s">
+        <v>115</v>
       </c>
       <c r="D104">
         <v>26</v>
       </c>
       <c r="E104" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -3005,13 +3389,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>111</v>
+        <v>120</v>
+      </c>
+      <c r="C105" t="s">
+        <v>115</v>
       </c>
       <c r="D105">
         <v>24</v>
       </c>
       <c r="E105" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -3019,13 +3406,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>112</v>
+        <v>121</v>
+      </c>
+      <c r="C106" t="s">
+        <v>122</v>
       </c>
       <c r="D106">
         <v>26</v>
       </c>
       <c r="E106" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -3033,13 +3423,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>113</v>
+        <v>123</v>
+      </c>
+      <c r="C107" t="s">
+        <v>236</v>
       </c>
       <c r="D107">
         <v>27</v>
       </c>
       <c r="E107" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -3047,13 +3440,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>114</v>
+        <v>124</v>
+      </c>
+      <c r="C108" t="s">
+        <v>125</v>
       </c>
       <c r="D108">
         <v>22</v>
       </c>
       <c r="E108" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -3061,13 +3457,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>187</v>
+        <v>224</v>
+      </c>
+      <c r="C109" t="s">
+        <v>125</v>
       </c>
       <c r="D109">
         <v>22</v>
       </c>
       <c r="E109" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -3075,13 +3474,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>115</v>
+        <v>126</v>
+      </c>
+      <c r="C110" t="s">
+        <v>125</v>
       </c>
       <c r="D110">
         <v>22</v>
       </c>
       <c r="E110" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -3089,13 +3491,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>116</v>
+        <v>127</v>
+      </c>
+      <c r="C111" t="s">
+        <v>125</v>
       </c>
       <c r="D111">
         <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -3103,13 +3508,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>117</v>
+        <v>128</v>
+      </c>
+      <c r="C112" t="s">
+        <v>129</v>
       </c>
       <c r="D112">
         <v>27</v>
       </c>
       <c r="E112" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -3117,13 +3525,16 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>118</v>
+        <v>130</v>
+      </c>
+      <c r="C113" t="s">
+        <v>131</v>
       </c>
       <c r="D113">
         <v>27</v>
       </c>
       <c r="E113" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -3131,13 +3542,16 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>119</v>
+        <v>132</v>
+      </c>
+      <c r="C114" t="s">
+        <v>133</v>
       </c>
       <c r="D114">
         <v>20</v>
       </c>
       <c r="E114" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -3145,13 +3559,16 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>121</v>
+        <v>135</v>
+      </c>
+      <c r="C115" t="s">
+        <v>133</v>
       </c>
       <c r="D115">
         <v>20</v>
       </c>
       <c r="E115" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -3159,13 +3576,16 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>122</v>
+        <v>136</v>
+      </c>
+      <c r="C116" t="s">
+        <v>133</v>
       </c>
       <c r="D116">
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -3173,13 +3593,16 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>123</v>
+        <v>137</v>
+      </c>
+      <c r="C117" t="s">
+        <v>133</v>
       </c>
       <c r="D117">
         <v>29</v>
       </c>
       <c r="E117" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -3187,13 +3610,16 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>124</v>
+        <v>138</v>
+      </c>
+      <c r="C118" t="s">
+        <v>133</v>
       </c>
       <c r="D118">
         <v>30</v>
       </c>
       <c r="E118" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -3201,13 +3627,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>125</v>
+        <v>139</v>
+      </c>
+      <c r="C119" t="s">
+        <v>140</v>
       </c>
       <c r="D119">
         <v>28</v>
       </c>
       <c r="E119" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -3215,13 +3644,16 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>142</v>
+      </c>
+      <c r="C120" t="s">
+        <v>140</v>
       </c>
       <c r="D120">
         <v>28</v>
       </c>
       <c r="E120" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -3229,13 +3661,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>128</v>
+        <v>143</v>
+      </c>
+      <c r="C121" t="s">
+        <v>140</v>
       </c>
       <c r="D121">
         <v>28</v>
       </c>
       <c r="E121" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -3243,13 +3678,16 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>188</v>
+        <v>225</v>
+      </c>
+      <c r="C122" t="s">
+        <v>140</v>
       </c>
       <c r="D122">
         <v>28</v>
       </c>
       <c r="E122" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -3257,13 +3695,16 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>129</v>
+        <v>144</v>
+      </c>
+      <c r="C123" t="s">
+        <v>140</v>
       </c>
       <c r="D123">
         <v>28</v>
       </c>
       <c r="E123" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -3271,13 +3712,16 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>145</v>
+      </c>
+      <c r="C124" t="s">
+        <v>140</v>
       </c>
       <c r="D124">
         <v>28</v>
       </c>
       <c r="E124" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -3285,13 +3729,16 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>146</v>
+      </c>
+      <c r="C125" t="s">
+        <v>140</v>
       </c>
       <c r="D125">
         <v>30</v>
       </c>
       <c r="E125" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -3299,13 +3746,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>189</v>
+        <v>226</v>
+      </c>
+      <c r="C126" t="s">
+        <v>140</v>
       </c>
       <c r="D126">
         <v>32</v>
       </c>
       <c r="E126" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
@@ -3313,13 +3763,16 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>147</v>
+      </c>
+      <c r="C127" t="s">
+        <v>140</v>
       </c>
       <c r="D127">
         <v>32</v>
       </c>
       <c r="E127" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -3327,13 +3780,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>133</v>
+        <v>148</v>
+      </c>
+      <c r="C128" t="s">
+        <v>149</v>
       </c>
       <c r="D128">
         <v>38</v>
       </c>
       <c r="E128" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -3341,13 +3797,16 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>134</v>
+        <v>150</v>
+      </c>
+      <c r="C129" t="s">
+        <v>151</v>
       </c>
       <c r="D129">
         <v>39</v>
       </c>
       <c r="E129" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -3355,13 +3814,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>135</v>
+        <v>152</v>
+      </c>
+      <c r="C130" t="s">
+        <v>153</v>
       </c>
       <c r="D130">
         <v>38</v>
       </c>
       <c r="E130" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -3369,13 +3831,16 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>136</v>
+        <v>154</v>
+      </c>
+      <c r="C131" t="s">
+        <v>155</v>
       </c>
       <c r="D131">
         <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -3383,13 +3848,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>138</v>
+        <v>157</v>
+      </c>
+      <c r="C132" t="s">
+        <v>155</v>
       </c>
       <c r="D132">
         <v>24</v>
       </c>
       <c r="E132" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -3397,13 +3865,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>199</v>
+        <v>242</v>
+      </c>
+      <c r="C133" t="s">
+        <v>155</v>
       </c>
       <c r="D133">
         <v>26</v>
       </c>
       <c r="E133" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -3411,13 +3882,16 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>139</v>
+        <v>158</v>
+      </c>
+      <c r="C134" t="s">
+        <v>159</v>
       </c>
       <c r="D134">
         <v>30</v>
       </c>
       <c r="E134" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -3425,13 +3899,16 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>141</v>
+        <v>161</v>
+      </c>
+      <c r="C135" t="s">
+        <v>159</v>
       </c>
       <c r="D135">
         <v>32</v>
       </c>
       <c r="E135" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -3439,13 +3916,16 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>142</v>
+        <v>162</v>
+      </c>
+      <c r="C136" t="s">
+        <v>163</v>
       </c>
       <c r="D136">
         <v>38</v>
       </c>
       <c r="E136" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -3453,13 +3933,16 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>143</v>
+        <v>164</v>
+      </c>
+      <c r="C137" t="s">
+        <v>165</v>
       </c>
       <c r="D137">
         <v>30</v>
       </c>
       <c r="E137" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -3467,13 +3950,16 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>145</v>
+        <v>167</v>
+      </c>
+      <c r="C138" t="s">
+        <v>165</v>
       </c>
       <c r="D138">
         <v>30</v>
       </c>
       <c r="E138" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
@@ -3481,13 +3967,16 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>146</v>
+        <v>168</v>
+      </c>
+      <c r="C139" t="s">
+        <v>165</v>
       </c>
       <c r="D139">
         <v>30</v>
       </c>
       <c r="E139" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -3495,13 +3984,16 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>169</v>
+      </c>
+      <c r="C140" t="s">
+        <v>165</v>
       </c>
       <c r="D140">
         <v>30</v>
       </c>
       <c r="E140" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
@@ -3509,13 +4001,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>208</v>
+        <v>227</v>
+      </c>
+      <c r="C141" t="s">
+        <v>165</v>
       </c>
       <c r="D141">
         <v>30</v>
       </c>
       <c r="E141" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -3523,13 +4018,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>207</v>
+        <v>170</v>
+      </c>
+      <c r="C142" t="s">
+        <v>165</v>
       </c>
       <c r="D142">
         <v>30</v>
       </c>
       <c r="E142" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -3537,13 +4035,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>190</v>
+        <v>228</v>
+      </c>
+      <c r="C143" t="s">
+        <v>165</v>
       </c>
       <c r="D143">
         <v>32</v>
       </c>
       <c r="E143" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -3551,13 +4052,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>148</v>
+        <v>171</v>
+      </c>
+      <c r="C144" t="s">
+        <v>172</v>
       </c>
       <c r="D144">
         <v>26</v>
       </c>
       <c r="E144" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
@@ -3565,13 +4069,16 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>150</v>
+        <v>174</v>
+      </c>
+      <c r="C145" t="s">
+        <v>172</v>
       </c>
       <c r="D145">
         <v>32</v>
       </c>
       <c r="E145" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
@@ -3579,13 +4086,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>151</v>
+        <v>175</v>
+      </c>
+      <c r="C146" t="s">
+        <v>176</v>
       </c>
       <c r="D146">
         <v>22</v>
       </c>
       <c r="E146" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
@@ -3593,13 +4103,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>153</v>
+        <v>178</v>
+      </c>
+      <c r="C147" t="s">
+        <v>176</v>
       </c>
       <c r="D147">
         <v>24</v>
       </c>
       <c r="E147" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
@@ -3607,13 +4120,16 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>154</v>
+        <v>179</v>
+      </c>
+      <c r="C148" t="s">
+        <v>176</v>
       </c>
       <c r="D148">
         <v>27</v>
       </c>
       <c r="E148" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
@@ -3621,16 +4137,16 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C149" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
       <c r="D149">
         <v>33</v>
       </c>
       <c r="E149" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
@@ -3638,13 +4154,16 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>157</v>
+        <v>182</v>
+      </c>
+      <c r="C150" t="s">
+        <v>183</v>
       </c>
       <c r="D150">
         <v>33</v>
       </c>
       <c r="E150" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
@@ -3652,13 +4171,16 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>182</v>
+        <v>219</v>
+      </c>
+      <c r="C151" t="s">
+        <v>214</v>
       </c>
       <c r="D151">
         <v>12</v>
       </c>
       <c r="E151" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
@@ -3666,13 +4188,16 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>183</v>
+        <v>220</v>
+      </c>
+      <c r="C152" t="s">
+        <v>214</v>
       </c>
       <c r="D152">
         <v>7</v>
       </c>
       <c r="E152" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
@@ -3680,13 +4205,16 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>184</v>
+        <v>221</v>
+      </c>
+      <c r="C153" t="s">
+        <v>214</v>
       </c>
       <c r="D153">
         <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
@@ -3694,13 +4222,16 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>159</v>
+        <v>185</v>
+      </c>
+      <c r="C154" t="s">
+        <v>215</v>
       </c>
       <c r="D154">
         <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
@@ -3708,13 +4239,16 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>160</v>
+        <v>186</v>
+      </c>
+      <c r="C155" t="s">
+        <v>215</v>
       </c>
       <c r="D155">
         <v>5</v>
       </c>
       <c r="E155" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
@@ -3722,13 +4256,16 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>179</v>
+        <v>216</v>
+      </c>
+      <c r="C156" t="s">
+        <v>214</v>
       </c>
       <c r="D156">
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
@@ -3736,13 +4273,16 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>180</v>
+        <v>217</v>
+      </c>
+      <c r="C157" t="s">
+        <v>214</v>
       </c>
       <c r="D157">
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
@@ -3750,13 +4290,16 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>181</v>
+        <v>218</v>
+      </c>
+      <c r="C158" t="s">
+        <v>214</v>
       </c>
       <c r="D158">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
@@ -3764,13 +4307,16 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>161</v>
+        <v>187</v>
+      </c>
+      <c r="C159" t="s">
+        <v>188</v>
       </c>
       <c r="D159">
         <v>3</v>
       </c>
       <c r="E159" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
@@ -3778,13 +4324,16 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>162</v>
+        <v>189</v>
+      </c>
+      <c r="C160" t="s">
+        <v>190</v>
       </c>
       <c r="D160">
         <v>13</v>
       </c>
       <c r="E160" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
@@ -3792,13 +4341,16 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>202</v>
+        <v>245</v>
+      </c>
+      <c r="C161" t="s">
+        <v>190</v>
       </c>
       <c r="D161">
         <v>11</v>
       </c>
       <c r="E161" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
@@ -3806,13 +4358,16 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>163</v>
+        <v>191</v>
+      </c>
+      <c r="C162" t="s">
+        <v>190</v>
       </c>
       <c r="D162">
         <v>7</v>
       </c>
       <c r="E162" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
@@ -3820,13 +4375,16 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>201</v>
+        <v>244</v>
+      </c>
+      <c r="C163" t="s">
+        <v>190</v>
       </c>
       <c r="D163">
         <v>6</v>
       </c>
       <c r="E163" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
@@ -3834,13 +4392,16 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>192</v>
+      </c>
+      <c r="C164" t="s">
+        <v>193</v>
       </c>
       <c r="D164">
         <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
@@ -3848,13 +4409,16 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>194</v>
+      </c>
+      <c r="C165" t="s">
+        <v>195</v>
       </c>
       <c r="D165">
         <v>6</v>
       </c>
       <c r="E165" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
@@ -3862,13 +4426,16 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>196</v>
+      </c>
+      <c r="C166" t="s">
+        <v>197</v>
       </c>
       <c r="D166">
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
@@ -3876,13 +4443,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>198</v>
+      </c>
+      <c r="C167" t="s">
+        <v>199</v>
       </c>
       <c r="D167">
         <v>15</v>
       </c>
       <c r="E167" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
@@ -3890,13 +4460,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>200</v>
+      </c>
+      <c r="C168" t="s">
+        <v>201</v>
       </c>
       <c r="D168">
         <v>17</v>
       </c>
       <c r="E168" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
@@ -3904,13 +4477,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>202</v>
+      </c>
+      <c r="C169" t="s">
+        <v>203</v>
       </c>
       <c r="D169">
         <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
@@ -3918,16 +4494,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="C170" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D170">
         <v>4</v>
       </c>
       <c r="E170" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
@@ -3935,16 +4511,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="C171" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="D171">
         <v>5</v>
       </c>
       <c r="E171" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
@@ -3952,16 +4528,16 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>177</v>
+        <v>211</v>
       </c>
       <c r="C172" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c r="D172">
         <v>26</v>
       </c>
       <c r="E172" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
